--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI55"/>
+  <dimension ref="A1:BI60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46099.53125</v>
+        <v>46099.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46099.54166666666</v>
+        <v>46099.53125</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,17 +2767,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46099.58333333334</v>
+        <v>46099.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,137 +3358,137 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>4.42</v>
       </c>
       <c r="S15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46099.60416666666</v>
+        <v>46099.58333333334</v>
       </c>
     </row>
     <row r="16">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.55</v>
       </c>
-      <c r="Q19" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="R19" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>4.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46099.61458333334</v>
+        <v>46099.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4398,10 +4398,10 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46099.625</v>
+        <v>46099.61458333334</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46099.64583333334</v>
+        <v>46099.625</v>
       </c>
     </row>
     <row r="22">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46099.66666666666</v>
+        <v>46099.64583333334</v>
       </c>
     </row>
     <row r="25">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46099.67708333334</v>
+        <v>46099.66666666666</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,142 +6711,142 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46099.69791666666</v>
+        <v>46099.66666666666</v>
       </c>
     </row>
     <row r="33">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46099.69791666666</v>
+        <v>46099.67708333334</v>
       </c>
     </row>
     <row r="34">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,142 +7105,142 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>2.49</v>
+        <v>4.17</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.66</v>
+        <v>2.33</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46099.70833333334</v>
+        <v>46099.69791666666</v>
       </c>
     </row>
     <row r="35">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46099.70833333334</v>
+        <v>46099.69791666666</v>
       </c>
     </row>
     <row r="36">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7747,10 +7747,10 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46099.72916666666</v>
+        <v>46099.70833333334</v>
       </c>
     </row>
     <row r="39">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46099.72916666666</v>
+        <v>46099.70833333334</v>
       </c>
     </row>
     <row r="40">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46099.75</v>
+        <v>46099.72916666666</v>
       </c>
     </row>
     <row r="45">
@@ -9219,27 +9219,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46099.77083333334</v>
+        <v>46099.72916666666</v>
       </c>
     </row>
     <row r="46">
@@ -9416,27 +9416,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46099.79166666666</v>
+        <v>46099.75</v>
       </c>
     </row>
     <row r="47">
@@ -9613,27 +9613,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46099.79166666666</v>
+        <v>46099.75</v>
       </c>
     </row>
     <row r="48">
@@ -9810,27 +9810,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46099.8125</v>
+        <v>46099.75</v>
       </c>
     </row>
     <row r="49">
@@ -10007,27 +10007,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46099.83333333334</v>
+        <v>46099.75</v>
       </c>
     </row>
     <row r="50">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46099.83333333334</v>
+        <v>46099.77083333334</v>
       </c>
     </row>
     <row r="51">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46099.875</v>
+        <v>46099.79166666666</v>
       </c>
     </row>
     <row r="52">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46099.875</v>
+        <v>46099.79166666666</v>
       </c>
     </row>
     <row r="53">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46099.875</v>
+        <v>46099.8125</v>
       </c>
     </row>
     <row r="54">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46099.89583333334</v>
+        <v>46099.83333333334</v>
       </c>
     </row>
     <row r="55">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,6 +11377,991 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
+        <v>46099.83333333334</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Buxoro</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dinamo Samarqand</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" s="3" t="n">
+        <v>46099.875</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI57" s="3" t="n">
+        <v>46099.875</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Andijan</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mash'al</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI58" s="3" t="n">
+        <v>46099.875</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI59" s="3" t="n">
+        <v>46099.89583333334</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI60" s="3" t="n">
         <v>46099.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="R37" t="n">
-        <v>10.4</v>
+        <v>2.49</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,16 +7741,16 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="R38" t="n">
-        <v>2.49</v>
+        <v>10.4</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,16 +7938,16 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="R37" t="n">
-        <v>2.49</v>
+        <v>10.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,16 +7741,16 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="R38" t="n">
-        <v>10.4</v>
+        <v>2.49</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,16 +7938,16 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G57" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7502,10 +7502,10 @@
         <v>1.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="R36" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7553,7 +7553,7 @@
         <v>1.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7699,10 +7699,10 @@
         <v>1.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.4</v>
+        <v>6.44</v>
       </c>
       <c r="R37" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
         <v>1.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7550,10 +7550,10 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7550,10 +7550,10 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.44</v>
+        <v>3.95</v>
       </c>
       <c r="R37" t="n">
-        <v>10.6</v>
+        <v>2.49</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,16 +7741,16 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.95</v>
+        <v>6.44</v>
       </c>
       <c r="R39" t="n">
-        <v>2.49</v>
+        <v>10.6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,16 +8135,16 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G58" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="R36" t="n">
-        <v>10.4</v>
+        <v>2.49</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,16 +7544,16 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="R37" t="n">
-        <v>2.49</v>
+        <v>10.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,16 +7741,16 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G58" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7747,10 +7747,10 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G58" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
         <v>3.15</v>
       </c>
       <c r="R30" t="n">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.78</v>
+        <v>1.97</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>2.49</v>
+        <v>3.45</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7747,10 +7747,10 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="R39" t="n">
-        <v>10.4</v>
+        <v>2.49</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,16 +8135,16 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R35" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="S35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.44</v>
+        <v>3.95</v>
       </c>
       <c r="R38" t="n">
-        <v>10.6</v>
+        <v>2.49</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,16 +7938,16 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.95</v>
+        <v>6.44</v>
       </c>
       <c r="R39" t="n">
-        <v>2.49</v>
+        <v>10.6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,16 +8135,16 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="S34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="R37" t="n">
-        <v>10.4</v>
+        <v>2.49</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,16 +7741,16 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="R38" t="n">
-        <v>2.49</v>
+        <v>10.4</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,16 +7938,16 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.97</v>
+        <v>1.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>6.44</v>
       </c>
       <c r="R36" t="n">
-        <v>3.45</v>
+        <v>10.6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7550,10 +7550,10 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="R37" t="n">
-        <v>2.49</v>
+        <v>10.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,16 +7741,16 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="R38" t="n">
-        <v>10.4</v>
+        <v>2.49</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,16 +7938,16 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.44</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>10.6</v>
+        <v>3.45</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G58" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R35" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="S35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46099.69791666666</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G57" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>10.4</v>
+        <v>3.45</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7747,10 +7747,10 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.97</v>
+        <v>1.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="R39" t="n">
-        <v>3.45</v>
+        <v>10.4</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="S34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="R38" t="n">
-        <v>2.49</v>
+        <v>10.4</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,16 +7938,16 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="R39" t="n">
-        <v>10.4</v>
+        <v>2.49</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,16 +8135,16 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7502,10 +7502,10 @@
         <v>1.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="R36" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7553,7 +7553,7 @@
         <v>1.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.97</v>
+        <v>2.78</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="R37" t="n">
-        <v>3.45</v>
+        <v>2.49</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>10.4</v>
+        <v>3.45</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.95</v>
+        <v>6.44</v>
       </c>
       <c r="R39" t="n">
-        <v>2.49</v>
+        <v>10.6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,16 +8135,16 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R35" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="S35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7502,10 +7502,10 @@
         <v>1.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.4</v>
+        <v>6.44</v>
       </c>
       <c r="R36" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7553,7 +7553,7 @@
         <v>1.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="R37" t="n">
-        <v>2.49</v>
+        <v>10.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,16 +7741,16 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.97</v>
+        <v>2.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="R38" t="n">
-        <v>3.45</v>
+        <v>2.49</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.44</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>10.6</v>
+        <v>3.45</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7502,10 +7502,10 @@
         <v>1.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="R36" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7553,7 +7553,7 @@
         <v>1.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7699,10 +7699,10 @@
         <v>1.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.4</v>
+        <v>6.44</v>
       </c>
       <c r="R37" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
         <v>1.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.78</v>
+        <v>1.97</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>2.49</v>
+        <v>3.45</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.97</v>
+        <v>2.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="R39" t="n">
-        <v>3.45</v>
+        <v>2.49</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,55 +11045,55 @@
         </is>
       </c>
       <c r="P54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R54" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
         <v>2</v>
       </c>
-      <c r="Q54" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R54" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AF54" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7502,10 +7502,10 @@
         <v>1.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.4</v>
+        <v>6.44</v>
       </c>
       <c r="R36" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7553,7 +7553,7 @@
         <v>1.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.44</v>
+        <v>3.95</v>
       </c>
       <c r="R37" t="n">
-        <v>10.6</v>
+        <v>2.49</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,16 +7741,16 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="R39" t="n">
-        <v>2.49</v>
+        <v>10.4</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,16 +8135,16 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R59" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R60" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7502,10 +7502,10 @@
         <v>1.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="R36" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7553,7 +7553,7 @@
         <v>1.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8093,10 +8093,10 @@
         <v>1.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.4</v>
+        <v>6.44</v>
       </c>
       <c r="R39" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8144,7 +8144,7 @@
         <v>1.95</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,14 +10454,14 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="Q51" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R51" t="n">
         <v>4.33</v>
       </c>
-      <c r="R51" t="n">
-        <v>6.5</v>
-      </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="R52" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R60" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="S34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="R36" t="n">
-        <v>10.4</v>
+        <v>2.49</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,16 +7544,16 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="R37" t="n">
-        <v>2.49</v>
+        <v>10.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,16 +7741,16 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R54" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,55 +11242,55 @@
         </is>
       </c>
       <c r="P55" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R55" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AF55" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R59" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R60" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="R36" t="n">
-        <v>2.49</v>
+        <v>10.4</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,16 +7544,16 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7699,10 +7699,10 @@
         <v>1.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.4</v>
+        <v>6.44</v>
       </c>
       <c r="R37" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
         <v>1.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.44</v>
+        <v>3.95</v>
       </c>
       <c r="R39" t="n">
-        <v>10.6</v>
+        <v>2.49</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,16 +8135,16 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="R51" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,14 +10651,14 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="Q52" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R52" t="n">
         <v>4.33</v>
       </c>
-      <c r="R52" t="n">
-        <v>6.5</v>
-      </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,55 +11045,55 @@
         </is>
       </c>
       <c r="P54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R54" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
         <v>2</v>
       </c>
-      <c r="Q54" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R54" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AF54" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R60" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI60"/>
+  <dimension ref="A1:BI58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2521,27 +2521,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46099.53125</v>
+        <v>46099.46875</v>
       </c>
     </row>
     <row r="12">
@@ -2718,27 +2718,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46099.54166666666</v>
+        <v>46099.46875</v>
       </c>
     </row>
     <row r="13">
@@ -2915,27 +2915,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46099.58333333334</v>
+        <v>46099.5</v>
       </c>
     </row>
     <row r="14">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46099.58333333334</v>
+        <v>46099.53125</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,17 +3358,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46099.58333333334</v>
+        <v>46099.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46099.60416666666</v>
+        <v>46099.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46099.60416666666</v>
+        <v>46099.58333333334</v>
       </c>
     </row>
     <row r="18">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46099.60416666666</v>
+        <v>46099.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4398,10 +4398,10 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46099.61458333334</v>
+        <v>46099.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46099.625</v>
+        <v>46099.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46099.64583333334</v>
+        <v>46099.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4989,10 +4989,10 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46099.64583333334</v>
+        <v>46099.61458333334</v>
       </c>
     </row>
     <row r="24">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46099.64583333334</v>
+        <v>46099.625</v>
       </c>
     </row>
     <row r="25">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46099.66666666666</v>
+        <v>46099.64583333334</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46099.66666666666</v>
+        <v>46099.64583333334</v>
       </c>
     </row>
     <row r="27">
@@ -5673,27 +5673,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46099.66666666666</v>
+        <v>46099.64583333334</v>
       </c>
     </row>
     <row r="28">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R31" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46099.67708333334</v>
+        <v>46099.66666666666</v>
       </c>
     </row>
     <row r="34">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46099.69791666666</v>
+        <v>46099.66666666666</v>
       </c>
     </row>
     <row r="35">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,142 +7302,142 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.74</v>
+        <v>2.44</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>4.17</v>
+        <v>2.92</v>
       </c>
       <c r="S35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46099.69791666666</v>
+        <v>46099.66666666666</v>
       </c>
     </row>
     <row r="36">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7550,10 +7550,10 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46099.70833333334</v>
+        <v>46099.67708333334</v>
       </c>
     </row>
     <row r="37">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,142 +7696,142 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.44</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
-        <v>10.6</v>
+        <v>4.17</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN37" t="n">
         <v>1.95</v>
       </c>
-      <c r="AH37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0</v>
-      </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46099.70833333334</v>
+        <v>46099.69791666666</v>
       </c>
     </row>
     <row r="38">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R38" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46099.70833333334</v>
+        <v>46099.69791666666</v>
       </c>
     </row>
     <row r="39">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46099.72916666666</v>
+        <v>46099.70833333334</v>
       </c>
     </row>
     <row r="41">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46099.72916666666</v>
+        <v>46099.70833333334</v>
       </c>
     </row>
     <row r="42">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8732,10 +8732,10 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46099.72916666666</v>
+        <v>46099.70833333334</v>
       </c>
     </row>
     <row r="43">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46099.875</v>
+        <v>46099.89583333334</v>
       </c>
     </row>
     <row r="58">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11968,400 +11968,6 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46099.875</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Vasco da Gama</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N59" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P59" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R59" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI59" s="3" t="n">
-        <v>46099.89583333334</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P60" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R60" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI60" s="3" t="n">
         <v>46099.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.26</v>
+        <v>3.64</v>
       </c>
       <c r="R25" t="n">
-        <v>2.41</v>
+        <v>2.11</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.44</v>
+        <v>3.4</v>
       </c>
       <c r="R40" t="n">
-        <v>10.6</v>
+        <v>3.45</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.97</v>
+        <v>1.31</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="R41" t="n">
-        <v>3.45</v>
+        <v>10.4</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8535,10 +8535,10 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8684,10 +8684,10 @@
         <v>1.31</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.4</v>
+        <v>6.44</v>
       </c>
       <c r="R42" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8735,7 +8735,7 @@
         <v>1.95</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R54" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,55 +11242,55 @@
         </is>
       </c>
       <c r="P55" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R55" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AF55" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R32" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R37" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="S37" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R38" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46099.69791666666</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="R39" t="n">
-        <v>2.49</v>
+        <v>10.4</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,16 +8135,16 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.97</v>
+        <v>1.31</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.4</v>
+        <v>6.44</v>
       </c>
       <c r="R40" t="n">
-        <v>3.45</v>
+        <v>10.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="R41" t="n">
-        <v>10.4</v>
+        <v>3.45</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8535,10 +8535,10 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.44</v>
+        <v>3.95</v>
       </c>
       <c r="R42" t="n">
-        <v>10.6</v>
+        <v>2.49</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,16 +8726,16 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,14 +10454,14 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="Q51" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R51" t="n">
         <v>4.33</v>
       </c>
-      <c r="R51" t="n">
-        <v>6.5</v>
-      </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="R52" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R58" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>4.42</v>
+        <v>6</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN17" t="n">
         <v>2.5</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.28</v>
+        <v>4.35</v>
       </c>
       <c r="R23" t="n">
-        <v>5.59</v>
+        <v>4.84</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS23" t="n">
         <v>1.66</v>
       </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="R24" t="n">
-        <v>5.32</v>
+        <v>5.62</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5216,52 +5216,52 @@
         <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU24" t="n">
         <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.85</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>2.11</v>
+        <v>3.4</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,34 +6317,34 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -6356,91 +6356,91 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB30" t="n">
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7129,10 +7129,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -7144,40 +7144,40 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7186,49 +7186,49 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB34" t="n">
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7508,70 +7508,70 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7613,19 +7613,19 @@
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.31</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="R39" t="n">
-        <v>10.4</v>
+        <v>2.52</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.44</v>
+        <v>6.5</v>
       </c>
       <c r="R40" t="n">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.97</v>
+        <v>1.32</v>
       </c>
       <c r="Q41" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U41" t="n">
+        <v>7</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W41" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN41" t="n">
         <v>3.4</v>
       </c>
-      <c r="R41" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>0</v>
-      </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="R42" t="n">
-        <v>2.49</v>
+        <v>4.7</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10454,79 +10454,79 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R51" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -10568,19 +10568,19 @@
         <v>0</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10651,79 +10651,79 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="R52" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10765,19 +10765,19 @@
         <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R53" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,79 +11045,79 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R54" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
@@ -11159,19 +11159,19 @@
         <v>0</v>
       </c>
       <c r="BB54" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC54" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD54" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF54" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,80 +11242,80 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AE55" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AF55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN55" t="n">
         <v>1.71</v>
       </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>0</v>
-      </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
@@ -11356,19 +11356,19 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,79 +11636,79 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R57" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
@@ -11750,19 +11750,19 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,79 +11833,79 @@
         </is>
       </c>
       <c r="P58" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R58" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W58" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AE58" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q58" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R58" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF58" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
@@ -11947,19 +11947,19 @@
         <v>0</v>
       </c>
       <c r="BB58" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC58" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BD58" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="BE58" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF58" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1825,22 +1825,22 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.25</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>3.7</v>
       </c>
       <c r="S16" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,28 +3756,28 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.47</v>
+        <v>5.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="R17" t="n">
-        <v>6</v>
+        <v>1.58</v>
       </c>
       <c r="S17" t="n">
-        <v>1.98</v>
+        <v>5.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>2.04</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="X17" t="n">
         <v>2.39</v>
@@ -3786,13 +3786,13 @@
         <v>1.51</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC17" t="n">
         <v>1.2</v>
@@ -3801,88 +3801,88 @@
         <v>4.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
         <v>2.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="AJ17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.18</v>
       </c>
-      <c r="AK17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AN17" t="n">
-        <v>2.5</v>
+        <v>1.13</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.29</v>
+        <v>3.15</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.2</v>
+        <v>1.46</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN18" t="n">
         <v>2.5</v>
       </c>
-      <c r="AF18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="Q20" t="n">
         <v>2.8</v>
@@ -4410,7 +4410,7 @@
         <v>1.04</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AL20" t="n">
         <v>1.57</v>
@@ -4461,10 +4461,10 @@
         <v>1.78</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BD20" t="n">
         <v>2.63</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>5.62</v>
+        <v>5.86</v>
       </c>
       <c r="S24" t="n">
         <v>2.02</v>
@@ -5153,10 +5153,10 @@
         <v>5.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="X24" t="n">
         <v>2.38</v>
@@ -5192,16 +5192,16 @@
         <v>1.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK24" t="n">
         <v>1.7</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AM24" t="n">
         <v>1.2</v>
@@ -5249,16 +5249,16 @@
         <v>3.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BF24" t="n">
         <v>1.22</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.62</v>
+        <v>1.96</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R27" t="n">
         <v>3.4</v>
       </c>
-      <c r="R27" t="n">
-        <v>2.38</v>
-      </c>
       <c r="S27" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.96</v>
+        <v>2.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S28" t="n">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="X28" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="Z28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AD28" t="n">
-        <v>5.9</v>
+        <v>2.95</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.66</v>
+        <v>1.66</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.02</v>
+        <v>3.65</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.71</v>
+        <v>1.23</v>
       </c>
       <c r="AI28" t="n">
-        <v>3.14</v>
+        <v>6.75</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL28" t="n">
         <v>1.86</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>3.72</v>
+        <v>1.42</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.17</v>
+        <v>2.75</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.68</v>
+        <v>2.7</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.57</v>
+        <v>2.02</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.97</v>
+        <v>1.63</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.05</v>
+        <v>2.25</v>
       </c>
       <c r="BA28" t="n">
-        <v>9.9</v>
+        <v>1.74</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.15</v>
+        <v>1.54</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6120,34 +6120,34 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.73</v>
+        <v>2.54</v>
       </c>
       <c r="R29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="U29" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="V29" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W29" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="X29" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z29" t="n">
         <v>8.699999999999999</v>
@@ -6159,91 +6159,91 @@
         <v>1.07</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AI29" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AV29" t="n">
         <v>1.98</v>
       </c>
-      <c r="AS29" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AW29" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="BB29" t="n">
         <v>1.3</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="BD29" t="n">
         <v>3.22</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="BF29" t="n">
         <v>1.1</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,130 +6317,130 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="S30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG30" t="n">
         <v>3.1</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AI30" t="n">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.75</v>
+        <v>2.17</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA30" t="n">
         <v>2.02</v>
       </c>
-      <c r="AW30" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>1.74</v>
-      </c>
       <c r="BB30" t="n">
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6720,124 +6720,124 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7129,10 +7129,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -7144,40 +7144,40 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7186,49 +7186,49 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7544,7 +7544,7 @@
         <v>4.8</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AF36" t="n">
         <v>2.35</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R37" t="n">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="S37" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="T37" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U37" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="V37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY37" t="n">
         <v>1.31</v>
-      </c>
-      <c r="W37" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.55</v>
       </c>
       <c r="AZ37" t="n">
         <v>1.37</v>
       </c>
       <c r="BA37" t="n">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="BB37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF37" t="n">
         <v>1.17</v>
       </c>
-      <c r="BC37" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>4.17</v>
+        <v>3.7</v>
       </c>
       <c r="S38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL38" t="n">
         <v>2.19</v>
       </c>
-      <c r="T38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U38" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W38" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AM38" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AO38" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.56</v>
+        <v>1.84</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.52</v>
+        <v>2.28</v>
       </c>
       <c r="AU38" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.42</v>
+        <v>1.84</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.38</v>
+        <v>3.4</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="BD38" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46099.69791666666</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.7</v>
+        <v>6.25</v>
       </c>
       <c r="R39" t="n">
-        <v>2.52</v>
+        <v>8.6</v>
       </c>
       <c r="S39" t="n">
-        <v>3.06</v>
+        <v>1.67</v>
       </c>
       <c r="T39" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U39" t="n">
+        <v>7</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL39" t="n">
         <v>2.3</v>
       </c>
-      <c r="U39" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W39" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Y39" t="n">
+      <c r="AM39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ39" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z39" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC39" t="n">
+      <c r="AR39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD39" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN39" t="n">
+      <c r="BA39" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BC39" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BD39" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.25</v>
+        <v>3.7</v>
       </c>
       <c r="R41" t="n">
-        <v>8.6</v>
+        <v>2.52</v>
       </c>
       <c r="S41" t="n">
-        <v>1.67</v>
+        <v>3.06</v>
       </c>
       <c r="T41" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="U41" t="n">
-        <v>7</v>
+        <v>2.98</v>
       </c>
       <c r="V41" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="W41" t="n">
-        <v>4.65</v>
+        <v>3.42</v>
       </c>
       <c r="X41" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC41" t="n">
         <v>1.91</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR41" t="n">
+      <c r="BD41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE41" t="n">
         <v>1.83</v>
       </c>
-      <c r="AS41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BF41" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8681,22 +8681,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R42" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="S42" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="T42" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="U42" t="n">
-        <v>5.23</v>
+        <v>4.75</v>
       </c>
       <c r="V42" t="n">
         <v>1.37</v>
@@ -8720,13 +8720,13 @@
         <v>1</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF42" t="n">
         <v>1.82</v>
@@ -8738,19 +8738,19 @@
         <v>1.26</v>
       </c>
       <c r="AI42" t="n">
-        <v>6.25</v>
+        <v>6.65</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK42" t="n">
         <v>1.84</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AN42" t="n">
         <v>2.03</v>
@@ -8759,55 +8759,55 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="AU42" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="BA42" t="n">
-        <v>3.66</v>
+        <v>3.24</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R51" t="n">
-        <v>4.6</v>
+        <v>6.3</v>
       </c>
       <c r="S51" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="T51" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U51" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="V51" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W51" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="X51" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.65</v>
+        <v>5.55</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB51" t="n">
         <v>1</v>
       </c>
       <c r="AC51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM51" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD51" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL51" t="n">
+      <c r="AN51" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC51" t="n">
         <v>2</v>
       </c>
-      <c r="AM51" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>2.07</v>
-      </c>
       <c r="BD51" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="S52" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="T52" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="V52" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W52" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="X52" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Z52" t="n">
-        <v>5.55</v>
+        <v>6.25</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB52" t="n">
         <v>1</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AI52" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AM52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN52" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF52" t="n">
         <v>1.18</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10848,19 +10848,19 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="R53" t="n">
         <v>2.65</v>
       </c>
       <c r="S53" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="T53" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U53" t="n">
         <v>3.2</v>
@@ -10869,112 +10869,112 @@
         <v>1.4</v>
       </c>
       <c r="W53" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="X53" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Y53" t="n">
         <v>1.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG53" t="n">
         <v>3.44</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI53" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK53" t="n">
         <v>1.8</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BA53" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BC53" t="n">
         <v>2.27</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="BE53" t="n">
         <v>1.59</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11045,43 +11045,43 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R54" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="S54" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="T54" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="U54" t="n">
-        <v>5.45</v>
+        <v>4.5</v>
       </c>
       <c r="V54" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W54" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="X54" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Y54" t="n">
         <v>1.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC54" t="n">
         <v>1.28</v>
@@ -11096,82 +11096,82 @@
         <v>1.72</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL54" t="n">
         <v>1.8</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AN54" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU54" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11242,67 +11242,67 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q55" t="n">
         <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="S55" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="T55" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="U55" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="V55" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W55" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="X55" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z55" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AE55" t="n">
         <v>2.08</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AH55" t="n">
         <v>1.22</v>
       </c>
       <c r="AI55" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK55" t="n">
         <v>1.83</v>
@@ -11311,64 +11311,64 @@
         <v>1.85</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AN55" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T57" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R57" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.09</v>
-      </c>
       <c r="U57" t="n">
-        <v>3.92</v>
+        <v>2.95</v>
       </c>
       <c r="V57" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W57" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="X57" t="n">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z57" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB57" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB57" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH57" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AI57" t="n">
-        <v>5.65</v>
+        <v>7</v>
       </c>
       <c r="AJ57" t="n">
         <v>1.08</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL57" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AM57" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AN57" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS57" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BB57" t="n">
         <v>1.22</v>
       </c>
       <c r="BC57" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,133 +11833,133 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="Q58" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R58" t="n">
         <v>3.25</v>
       </c>
-      <c r="R58" t="n">
-        <v>2.37</v>
-      </c>
       <c r="S58" t="n">
-        <v>3.62</v>
+        <v>2.7</v>
       </c>
       <c r="T58" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="U58" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="V58" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W58" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV58" t="n">
         <v>2.8</v>
       </c>
-      <c r="X58" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>0</v>
-      </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC58" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="BD58" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="X2" t="n">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.9</v>
+        <v>7.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AF2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1.53</v>
       </c>
-      <c r="AG2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BF2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC3" t="n">
         <v>2.5</v>
       </c>
-      <c r="X3" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BD3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -2001,16 +2001,16 @@
         <v>3.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="X8" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
         <v>9</v>
@@ -2040,10 +2040,10 @@
         <v>1.16</v>
       </c>
       <c r="AI8" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
         <v>1.91</v>
@@ -2055,7 +2055,7 @@
         <v>1.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,28 +3756,28 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.1</v>
+        <v>4.58</v>
       </c>
       <c r="R17" t="n">
-        <v>1.58</v>
+        <v>6.4</v>
       </c>
       <c r="S17" t="n">
-        <v>5.3</v>
+        <v>1.98</v>
       </c>
       <c r="T17" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="X17" t="n">
         <v>2.39</v>
@@ -3786,13 +3786,13 @@
         <v>1.51</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
         <v>1.2</v>
@@ -3801,88 +3801,88 @@
         <v>4.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
         <v>2.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="AH17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI17" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AR17" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="AT17" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.15</v>
+        <v>1.29</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.46</v>
+        <v>4.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,28 +3953,28 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.47</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>4.11</v>
       </c>
       <c r="R18" t="n">
-        <v>6</v>
+        <v>1.64</v>
       </c>
       <c r="S18" t="n">
-        <v>1.98</v>
+        <v>4.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U18" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="X18" t="n">
         <v>2.39</v>
@@ -3983,13 +3983,13 @@
         <v>1.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
         <v>1.2</v>
@@ -3998,73 +3998,73 @@
         <v>4.33</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1.65</v>
       </c>
-      <c r="AF18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ18" t="n">
+      <c r="AL18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1.18</v>
       </c>
-      <c r="AK18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AN18" t="n">
-        <v>2.5</v>
+        <v>1.17</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.29</v>
+        <v>3.15</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.2</v>
+        <v>1.46</v>
       </c>
       <c r="BB18" t="n">
         <v>1.2</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="R24" t="n">
-        <v>5.86</v>
+        <v>5.7</v>
       </c>
       <c r="S24" t="n">
         <v>2.02</v>
@@ -5153,10 +5153,10 @@
         <v>5.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W24" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="X24" t="n">
         <v>2.38</v>
@@ -5165,10 +5165,10 @@
         <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.45</v>
+        <v>5.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AB24" t="n">
         <v>1.03</v>
@@ -5189,19 +5189,19 @@
         <v>2.65</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
         <v>1.7</v>
       </c>
       <c r="AL24" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AM24" t="n">
         <v>1.2</v>
@@ -5252,13 +5252,13 @@
         <v>1.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BD24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF24" t="n">
         <v>1.22</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>2.09</v>
+        <v>2.46</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>2.59</v>
+        <v>2.98</v>
       </c>
       <c r="V25" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="X25" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.7</v>
+        <v>5.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AD25" t="n">
-        <v>5.35</v>
+        <v>3.75</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.49</v>
+        <v>1.91</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.58</v>
+        <v>5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.35</v>
+        <v>3.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R26" t="n">
-        <v>2.38</v>
+        <v>3.37</v>
       </c>
       <c r="S26" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.85</v>
+        <v>2.74</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="R27" t="n">
-        <v>3.4</v>
+        <v>2.09</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="Q28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="X28" t="n">
         <v>3.25</v>
       </c>
-      <c r="R28" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AI28" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AM28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BB28" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
       <c r="BC28" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="R29" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U29" t="n">
         <v>3.25</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U29" t="n">
-        <v>3.5</v>
-      </c>
       <c r="V29" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W29" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="X29" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AG29" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AI29" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AM29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN29" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.45</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6210,13 +6210,13 @@
         <v>2.8</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AU29" t="n">
         <v>2.63</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AW29" t="n">
         <v>1.61</v>
@@ -6225,28 +6225,28 @@
         <v>1.37</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.88</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.17</v>
-      </c>
       <c r="U30" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="X30" t="n">
-        <v>2.63</v>
+        <v>2.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK30" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.5</v>
+        <v>3.72</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AX30" t="n">
         <v>1.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.89</v>
+        <v>1.05</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.02</v>
+        <v>9.9</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6595,52 +6595,52 @@
         <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6720,124 +6720,124 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7520,13 +7520,13 @@
         <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X36" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Z36" t="n">
         <v>4.8</v>
@@ -7538,34 +7538,34 @@
         <v>1.02</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AI36" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AM36" t="n">
         <v>3.3</v>
@@ -7616,16 +7616,16 @@
         <v>1.17</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BD36" t="n">
         <v>4.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7699,7 +7699,7 @@
         <v>1.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
         <v>4.35</v>
@@ -7711,7 +7711,7 @@
         <v>2.25</v>
       </c>
       <c r="U37" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="V37" t="n">
         <v>1.38</v>
@@ -7741,10 +7741,10 @@
         <v>3.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG37" t="n">
         <v>3.2</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.25</v>
+        <v>3.7</v>
       </c>
       <c r="R39" t="n">
-        <v>8.6</v>
+        <v>2.52</v>
       </c>
       <c r="S39" t="n">
-        <v>1.67</v>
+        <v>3.06</v>
       </c>
       <c r="T39" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="U39" t="n">
-        <v>7</v>
+        <v>2.98</v>
       </c>
       <c r="V39" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="W39" t="n">
-        <v>4.65</v>
+        <v>3.42</v>
       </c>
       <c r="X39" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC39" t="n">
         <v>1.91</v>
       </c>
-      <c r="Z39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR39" t="n">
+      <c r="BD39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE39" t="n">
         <v>1.83</v>
       </c>
-      <c r="AS39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BF39" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.7</v>
+        <v>6.25</v>
       </c>
       <c r="R41" t="n">
-        <v>2.52</v>
+        <v>8.6</v>
       </c>
       <c r="S41" t="n">
-        <v>3.06</v>
+        <v>1.67</v>
       </c>
       <c r="T41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U41" t="n">
+        <v>7</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W41" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL41" t="n">
         <v>2.3</v>
       </c>
-      <c r="U41" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W41" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Y41" t="n">
+      <c r="AM41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ41" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z41" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC41" t="n">
+      <c r="AR41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ41" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD41" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN41" t="n">
+      <c r="BA41" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BC41" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BD41" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R57" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W57" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X57" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV57" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q57" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R57" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="S57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T57" t="n">
+      <c r="AW57" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC57" t="n">
         <v>2.1</v>
       </c>
-      <c r="U57" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W57" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD57" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,133 +11833,133 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="R58" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="S58" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="T58" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U58" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="V58" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W58" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="X58" t="n">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z58" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA58" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB58" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB58" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD58" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF58" t="n">
+      <c r="AQ58" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW58" t="n">
         <v>1.83</v>
       </c>
-      <c r="AG58" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH58" t="n">
+      <c r="AX58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY58" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI58" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR58" t="n">
+      <c r="AZ58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE58" t="n">
         <v>1.62</v>
       </c>
-      <c r="AS58" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB58" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC58" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD58" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE58" t="n">
-        <v>1.69</v>
-      </c>
       <c r="BF58" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC2" t="n">
         <v>2.5</v>
       </c>
-      <c r="X2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BD2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD3" t="n">
         <v>3.6</v>
       </c>
-      <c r="T3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="BE3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,73 +1589,73 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="X6" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB6" t="n">
         <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
         <v>1.36</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="R8" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="S8" t="n">
         <v>2.85</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,28 +3756,28 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.47</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.58</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>6.4</v>
+        <v>1.57</v>
       </c>
       <c r="S17" t="n">
-        <v>1.98</v>
+        <v>4.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="X17" t="n">
         <v>2.39</v>
@@ -3786,10 +3786,10 @@
         <v>1.51</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB17" t="n">
         <v>1.03</v>
@@ -3801,73 +3801,73 @@
         <v>4.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
         <v>2.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AJ17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.18</v>
       </c>
-      <c r="AK17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AN17" t="n">
-        <v>2.5</v>
+        <v>1.17</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.29</v>
+        <v>3.15</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.2</v>
+        <v>1.46</v>
       </c>
       <c r="BB17" t="n">
         <v>1.2</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,28 +3953,28 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>1.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.11</v>
+        <v>4.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.64</v>
+        <v>5.95</v>
       </c>
       <c r="S18" t="n">
-        <v>4.9</v>
+        <v>1.98</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="X18" t="n">
         <v>2.39</v>
@@ -3983,10 +3983,10 @@
         <v>1.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AB18" t="n">
         <v>1.03</v>
@@ -3998,73 +3998,73 @@
         <v>4.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="AH18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AR18" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="AT18" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.15</v>
+        <v>1.29</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.46</v>
+        <v>4.2</v>
       </c>
       <c r="BB18" t="n">
         <v>1.2</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4941,10 +4941,10 @@
         <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="R23" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="S23" t="n">
         <v>2.03</v>
@@ -4965,7 +4965,7 @@
         <v>2.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Z23" t="n">
         <v>4.2</v>
@@ -4977,16 +4977,16 @@
         <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AD23" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
         <v>1.37</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AG23" t="n">
         <v>2</v>
@@ -5004,10 +5004,10 @@
         <v>1.49</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AN23" t="n">
         <v>2.4</v>
@@ -5016,46 +5016,46 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AX23" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AZ23" t="n">
         <v>1.27</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="BB23" t="n">
         <v>1.12</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BD23" t="n">
         <v>5.5</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.92</v>
+        <v>2.74</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="R26" t="n">
-        <v>3.37</v>
+        <v>2.09</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.74</v>
+        <v>1.92</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="R27" t="n">
-        <v>2.09</v>
+        <v>3.37</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF27" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6326,124 +6326,124 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.88</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.11</v>
-      </c>
       <c r="U31" t="n">
-        <v>3.97</v>
+        <v>7</v>
       </c>
       <c r="V31" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>2.81</v>
+        <v>4.3</v>
       </c>
       <c r="X31" t="n">
-        <v>2.73</v>
+        <v>2.04</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z31" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC31" t="n">
+      <c r="AF31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD31" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK31" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.5</v>
+        <v>3.72</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AX31" t="n">
         <v>1.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.89</v>
+        <v>1.05</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.02</v>
+        <v>9.9</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6792,52 +6792,52 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q37" t="n">
         <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="S37" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="T37" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="U37" t="n">
-        <v>4.55</v>
+        <v>3.65</v>
       </c>
       <c r="V37" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="W37" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="X37" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC37" t="n">
         <v>1.22</v>
       </c>
       <c r="AD37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA37" t="n">
         <v>3.4</v>
       </c>
-      <c r="AE37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO37" t="n">
+      <c r="BB37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF37" t="n">
         <v>1.21</v>
       </c>
-      <c r="AP37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BG37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" t="n">
         <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="S38" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="T38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV38" t="n">
         <v>2.38</v>
       </c>
-      <c r="U38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="V38" t="n">
+      <c r="AW38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY38" t="n">
         <v>1.31</v>
       </c>
-      <c r="W38" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
+      <c r="AZ38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF38" t="n">
         <v>1.17</v>
       </c>
-      <c r="AQ38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR38" t="n">
+      <c r="BG38" t="n">
         <v>1.53</v>
       </c>
-      <c r="AS38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>0</v>
-      </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46099.69791666666</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="Q39" t="n">
         <v>3.7</v>
       </c>
       <c r="R39" t="n">
-        <v>2.52</v>
+        <v>4.5</v>
       </c>
       <c r="S39" t="n">
-        <v>3.06</v>
+        <v>2.29</v>
       </c>
       <c r="T39" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U39" t="n">
-        <v>2.98</v>
+        <v>4.75</v>
       </c>
       <c r="V39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="n">
         <v>1.3</v>
       </c>
-      <c r="W39" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AD39" t="n">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AH39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>1.42</v>
       </c>
-      <c r="AI39" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ39" t="n">
+      <c r="BA39" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BF39" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q40" t="n">
         <v>6.5</v>
       </c>
       <c r="R40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S40" t="n">
         <v>1.62</v>
@@ -8308,7 +8308,7 @@
         <v>1.18</v>
       </c>
       <c r="W40" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="X40" t="n">
         <v>1.95</v>
@@ -8329,13 +8329,13 @@
         <v>1.04</v>
       </c>
       <c r="AD40" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF40" t="n">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="AG40" t="n">
         <v>1.88</v>
@@ -8350,13 +8350,13 @@
         <v>1.38</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AN40" t="n">
         <v>3.6</v>
@@ -8365,43 +8365,43 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AU40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="AW40" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="AX40" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BA40" t="n">
         <v>8.5</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BC40" t="n">
         <v>1.6</v>
@@ -8410,7 +8410,7 @@
         <v>7.4</v>
       </c>
       <c r="BE40" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="BF40" t="n">
         <v>1.46</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.25</v>
+        <v>3.75</v>
       </c>
       <c r="R41" t="n">
-        <v>8.6</v>
+        <v>2.57</v>
       </c>
       <c r="S41" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="U41" t="n">
-        <v>7</v>
+        <v>3.02</v>
       </c>
       <c r="V41" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="W41" t="n">
-        <v>4.65</v>
+        <v>3.36</v>
       </c>
       <c r="X41" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AD41" t="n">
-        <v>7</v>
+        <v>3.84</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.33</v>
+        <v>1.76</v>
       </c>
       <c r="AF41" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.72</v>
+        <v>5.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="AK41" t="n">
         <v>1.6</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AM41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
         <v>1.13</v>
       </c>
-      <c r="AN41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AQ41" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AT41" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AZ41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB41" t="n">
         <v>1.2</v>
       </c>
-      <c r="BA41" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BC41" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="BD41" t="n">
-        <v>7.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>2.46</v>
+        <v>1.8</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.45</v>
+        <v>1.21</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="R42" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="S42" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.33</v>
-      </c>
       <c r="T42" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>4.75</v>
+        <v>7.1</v>
       </c>
       <c r="V42" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="W42" t="n">
-        <v>2.81</v>
+        <v>4.65</v>
       </c>
       <c r="X42" t="n">
-        <v>2.77</v>
+        <v>1.85</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="Z42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD42" t="n">
         <v>7</v>
       </c>
-      <c r="AA42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AE42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AI42" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR42" t="n">
         <v>1.82</v>
       </c>
-      <c r="AG42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
+      <c r="AS42" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY42" t="n">
         <v>1.33</v>
       </c>
-      <c r="AQ42" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AZ42" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="BA42" t="n">
-        <v>3.24</v>
+        <v>5.2</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.4</v>
+        <v>7.9</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>6.3</v>
+        <v>4.6</v>
       </c>
       <c r="S51" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="T51" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="V51" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W51" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="X51" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="Z51" t="n">
-        <v>5.55</v>
+        <v>6.25</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB51" t="n">
         <v>1</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.74</v>
+        <v>3.55</v>
       </c>
       <c r="AE51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK51" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF51" t="n">
+      <c r="AL51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS51" t="n">
         <v>2.05</v>
       </c>
-      <c r="AG51" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AT51" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AU51" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AV51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA51" t="n">
         <v>2.85</v>
       </c>
-      <c r="AW51" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA51" t="n">
+      <c r="BB51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD51" t="n">
         <v>3.7</v>
       </c>
-      <c r="BB51" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE51" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R52" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="S52" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="T52" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U52" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="V52" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W52" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="X52" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.25</v>
+        <v>5.55</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB52" t="n">
         <v>1</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.55</v>
+        <v>3.74</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AI52" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="AJ52" t="n">
         <v>1.11</v>
       </c>
       <c r="AK52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX52" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL52" t="n">
+      <c r="AY52" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC52" t="n">
         <v>2</v>
       </c>
-      <c r="AM52" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BD52" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>3</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG53" t="n">
         <v>3.44</v>
@@ -11048,10 +11048,10 @@
         <v>1.76</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R54" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="S54" t="n">
         <v>2.3</v>
@@ -11093,7 +11093,7 @@
         <v>2.07</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG54" t="n">
         <v>3.7</v>
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q55" t="n">
         <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="S55" t="n">
         <v>2.7</v>
@@ -11266,13 +11266,13 @@
         <v>2.8</v>
       </c>
       <c r="X55" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z55" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA55" t="n">
         <v>1.03</v>
@@ -11287,7 +11287,7 @@
         <v>3</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AF55" t="n">
         <v>1.67</v>
@@ -11329,7 +11329,7 @@
         <v>1.95</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AT55" t="n">
         <v>3.3</v>
@@ -11338,7 +11338,7 @@
         <v>3</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AW55" t="n">
         <v>1.75</v>
@@ -11347,10 +11347,10 @@
         <v>1.46</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BA55" t="n">
         <v>2.9</v>
@@ -11359,7 +11359,7 @@
         <v>1.3</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BD55" t="n">
         <v>3.3</v>
@@ -11642,7 +11642,7 @@
         <v>3.45</v>
       </c>
       <c r="R57" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="S57" t="n">
         <v>2.7</v>
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="Q58" t="n">
         <v>3.25</v>
@@ -11881,7 +11881,7 @@
         <v>2.05</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG58" t="n">
         <v>3.38</v>
@@ -11947,7 +11947,7 @@
         <v>1.94</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC58" t="n">
         <v>2.2</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.87</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>4.64</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="X2" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.9</v>
+        <v>7.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AK2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL2" t="n">
         <v>1.95</v>
       </c>
-      <c r="AL2" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AM2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,80 +998,80 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC3" t="n">
         <v>1.44</v>
       </c>
-      <c r="W3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AD3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN3" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="R5" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="S5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>3.7</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>1.5</v>
       </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>3.7</v>
       </c>
       <c r="S17" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="R25" t="n">
-        <v>2.46</v>
+        <v>2.09</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="U25" t="n">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="W25" t="n">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="X25" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.85</v>
+        <v>4.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AI25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BD25" t="n">
         <v>5</v>
       </c>
-      <c r="AJ25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE25" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,80 +5529,80 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>2.09</v>
+        <v>2.46</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="V26" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="X26" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.7</v>
+        <v>5.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AD26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI26" t="n">
         <v>5</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AJ26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN26" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6326,124 +6326,124 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6523,124 +6523,124 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.13</v>
+        <v>3.24</v>
       </c>
       <c r="R35" t="n">
-        <v>4.6</v>
+        <v>4.98</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q37" t="n">
         <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="S37" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="T37" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="U37" t="n">
-        <v>3.65</v>
+        <v>4.55</v>
       </c>
       <c r="V37" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W37" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="X37" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC37" t="n">
         <v>1.22</v>
       </c>
       <c r="AD37" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AI37" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF37" t="n">
         <v>1.17</v>
       </c>
-      <c r="AQ37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
         <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="S38" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="T38" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="U38" t="n">
-        <v>4.55</v>
+        <v>3.65</v>
       </c>
       <c r="V38" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="W38" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="X38" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC38" t="n">
         <v>1.22</v>
       </c>
       <c r="AD38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA38" t="n">
         <v>3.4</v>
       </c>
-      <c r="AE38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO38" t="n">
+      <c r="BB38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF38" t="n">
         <v>1.21</v>
       </c>
-      <c r="AP38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BG38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46099.69791666666</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R39" t="n">
-        <v>4.5</v>
+        <v>2.57</v>
       </c>
       <c r="S39" t="n">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U39" t="n">
-        <v>4.75</v>
+        <v>3.02</v>
       </c>
       <c r="V39" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W39" t="n">
-        <v>2.81</v>
+        <v>3.36</v>
       </c>
       <c r="X39" t="n">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB39" t="n">
-        <v>1</v>
-      </c>
       <c r="AC39" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AD39" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA39" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>3.24</v>
-      </c>
       <c r="BB39" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="Q41" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="R41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W41" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z41" t="n">
         <v>3.75</v>
       </c>
-      <c r="R41" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U41" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W41" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AA41" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.84</v>
+        <v>7</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AI41" t="n">
-        <v>5.5</v>
+        <v>2.72</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AK41" t="n">
         <v>1.6</v>
       </c>
       <c r="AL41" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV41" t="n">
         <v>2.38</v>
       </c>
-      <c r="AM41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AW41" t="n">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="AX41" t="n">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="BA41" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.15</v>
+        <v>3.7</v>
       </c>
       <c r="R42" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="S42" t="n">
-        <v>1.68</v>
+        <v>2.29</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="U42" t="n">
-        <v>7.1</v>
+        <v>4.75</v>
       </c>
       <c r="V42" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="W42" t="n">
-        <v>4.65</v>
+        <v>2.81</v>
       </c>
       <c r="X42" t="n">
-        <v>1.85</v>
+        <v>2.77</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BB42" t="n">
         <v>1.25</v>
       </c>
-      <c r="AB42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AK42" t="n">
+      <c r="BC42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE42" t="n">
         <v>1.6</v>
       </c>
-      <c r="AL42" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AM42" t="n">
+      <c r="BF42" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>1.46</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,130 +10454,130 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R51" t="n">
-        <v>4.6</v>
+        <v>6.03</v>
       </c>
       <c r="S51" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T51" t="n">
         <v>2.3</v>
       </c>
-      <c r="T51" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U51" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="V51" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W51" t="n">
-        <v>2.89</v>
+        <v>3.22</v>
       </c>
       <c r="X51" t="n">
         <v>2.69</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB51" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI51" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX51" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
+      <c r="AY51" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB51" t="n">
         <v>1.22</v>
       </c>
-      <c r="AQ51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS51" t="n">
+      <c r="BC51" t="n">
         <v>2.05</v>
       </c>
-      <c r="AT51" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BD51" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BF51" t="n">
         <v>1.18</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="S52" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="T52" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="V52" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W52" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="X52" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="Z52" t="n">
-        <v>5.55</v>
+        <v>6.65</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB52" t="n">
         <v>1</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.74</v>
+        <v>3.55</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AI52" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AJ52" t="n">
         <v>1.11</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AN52" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AU52" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AV52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA52" t="n">
         <v>2.85</v>
       </c>
-      <c r="AW52" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA52" t="n">
+      <c r="BB52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD52" t="n">
         <v>3.7</v>
       </c>
-      <c r="BB52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE52" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10869,7 +10869,7 @@
         <v>1.4</v>
       </c>
       <c r="W53" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="X53" t="n">
         <v>2.94</v>
@@ -10878,13 +10878,13 @@
         <v>1.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC53" t="n">
         <v>1.33</v>
@@ -10902,13 +10902,13 @@
         <v>3.44</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AI53" t="n">
         <v>7.5</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK53" t="n">
         <v>1.8</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,124 +11045,124 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="S54" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="T54" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U54" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="V54" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W54" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="X54" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z54" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB54" t="n">
         <v>1.06</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI54" t="n">
         <v>7.5</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN54" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR54" t="n">
         <v>1.95</v>
       </c>
-      <c r="AO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AS54" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="AU54" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="AV54" t="n">
-        <v>3.15</v>
+        <v>2.23</v>
       </c>
       <c r="AW54" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.88</v>
+        <v>1.46</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="BA54" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="BB54" t="n">
         <v>1.3</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BD54" t="n">
         <v>3.3</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R55" t="n">
-        <v>3.5</v>
+        <v>5.02</v>
       </c>
       <c r="S55" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="T55" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U55" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="V55" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W55" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="X55" t="n">
-        <v>2.85</v>
+        <v>3.09</v>
       </c>
       <c r="Y55" t="n">
         <v>1.35</v>
       </c>
       <c r="Z55" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB55" t="n">
         <v>1.06</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AD55" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AE55" t="n">
         <v>2.07</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI55" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL55" t="n">
         <v>1.85</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AN55" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="AU55" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="BA55" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R57" t="n">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="S57" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="T57" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U57" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="V57" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W57" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="X57" t="n">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z57" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB57" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB57" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF57" t="n">
+      <c r="AQ57" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW57" t="n">
         <v>1.83</v>
       </c>
-      <c r="AG57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH57" t="n">
+      <c r="AX57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY57" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI57" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AZ57" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="BA57" t="n">
-        <v>2.65</v>
+        <v>1.94</v>
       </c>
       <c r="BB57" t="n">
         <v>1.25</v>
       </c>
       <c r="BC57" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,133 +11833,133 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.91</v>
+        <v>2.22</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R58" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="S58" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="T58" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W58" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG58" t="n">
         <v>2.95</v>
       </c>
-      <c r="V58" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W58" t="n">
+      <c r="AH58" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV58" t="n">
         <v>2.8</v>
       </c>
-      <c r="X58" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AW58" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AZ58" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.94</v>
+        <v>2.65</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC58" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="BD58" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W2" t="n">
         <v>2.55</v>
       </c>
-      <c r="T2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U2" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.73</v>
-      </c>
       <c r="X2" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="Y2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN2" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="Q3" t="n">
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.9</v>
+        <v>7.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AF3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.53</v>
       </c>
-      <c r="AG3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1231,31 +1231,31 @@
         <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
         <v>1.7</v>
@@ -1273,55 +1273,55 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB4" t="n">
         <v>1.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="R6" t="n">
-        <v>2.32</v>
+        <v>2.93</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="X6" t="n">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.06</v>
       </c>
       <c r="AK6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL6" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
         <v>1.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>3.7</v>
       </c>
       <c r="S16" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>3.7</v>
+        <v>1.57</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>1.5</v>
       </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6347,7 +6347,7 @@
         <v>1.69</v>
       </c>
       <c r="Z30" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA30" t="n">
         <v>1.19</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.08</v>
+        <v>2.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>3.15</v>
+        <v>2.61</v>
       </c>
       <c r="S32" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T32" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="U32" t="n">
-        <v>3.97</v>
+        <v>3.25</v>
       </c>
       <c r="V32" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W32" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="X32" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN32" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z32" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG32" t="n">
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD32" t="n">
         <v>3.1</v>
       </c>
-      <c r="AH32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BE32" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.84</v>
+        <v>2.08</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>2.61</v>
+        <v>3.15</v>
       </c>
       <c r="S34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG34" t="n">
         <v>3.1</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AH34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB34" t="n">
         <v>1.21</v>
       </c>
-      <c r="AI34" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC34" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
         <v>1.46</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AG36" t="n">
         <v>2.2</v>
@@ -7562,16 +7562,16 @@
         <v>1.22</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AM36" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q37" t="n">
         <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="S37" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="T37" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="U37" t="n">
-        <v>4.55</v>
+        <v>3.65</v>
       </c>
       <c r="V37" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="W37" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="X37" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC37" t="n">
         <v>1.22</v>
       </c>
       <c r="AD37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA37" t="n">
         <v>3.4</v>
       </c>
-      <c r="AE37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO37" t="n">
+      <c r="BB37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF37" t="n">
         <v>1.21</v>
       </c>
-      <c r="AP37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BG37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" t="n">
         <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="S38" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="T38" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="U38" t="n">
-        <v>3.65</v>
+        <v>4.55</v>
       </c>
       <c r="V38" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W38" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="X38" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC38" t="n">
         <v>1.22</v>
       </c>
       <c r="AD38" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AI38" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF38" t="n">
         <v>1.17</v>
       </c>
-      <c r="AQ38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46099.69791666666</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="Q39" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="R39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z39" t="n">
         <v>3.75</v>
       </c>
-      <c r="R39" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W39" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AA39" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.84</v>
+        <v>7</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AI39" t="n">
-        <v>5.5</v>
+        <v>2.72</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AK39" t="n">
         <v>1.6</v>
       </c>
       <c r="AL39" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV39" t="n">
         <v>2.38</v>
       </c>
-      <c r="AM39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AW39" t="n">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="AX39" t="n">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC40" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U40" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W40" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AD40" t="n">
-        <v>6.25</v>
+        <v>3.3</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="AF40" t="n">
-        <v>3.19</v>
+        <v>1.82</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.88</v>
+        <v>3.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.99</v>
+        <v>1.26</v>
       </c>
       <c r="AI40" t="n">
-        <v>3</v>
+        <v>6.65</v>
       </c>
       <c r="AJ40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX40" t="n">
         <v>1.38</v>
       </c>
-      <c r="AK40" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR40" t="n">
+      <c r="AY40" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ40" t="n">
         <v>1.42</v>
       </c>
-      <c r="AS40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>1.09</v>
-      </c>
       <c r="BA40" t="n">
-        <v>8.5</v>
+        <v>3.24</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="BC40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE40" t="n">
         <v>1.6</v>
       </c>
-      <c r="BD40" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BF40" t="n">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,130 +8484,130 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="R41" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="S41" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T41" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U41" t="n">
-        <v>7.1</v>
+        <v>6.57</v>
       </c>
       <c r="V41" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W41" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="X41" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AB41" t="n">
         <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AD41" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF41" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AK41" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC41" t="n">
         <v>1.6</v>
       </c>
-      <c r="AL41" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>1.54</v>
-      </c>
       <c r="BD41" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE41" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="BF41" t="n">
         <v>1.46</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R42" t="n">
-        <v>4.5</v>
+        <v>2.57</v>
       </c>
       <c r="S42" t="n">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U42" t="n">
-        <v>4.75</v>
+        <v>3.02</v>
       </c>
       <c r="V42" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W42" t="n">
-        <v>2.81</v>
+        <v>3.36</v>
       </c>
       <c r="X42" t="n">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB42" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB42" t="n">
-        <v>1</v>
-      </c>
       <c r="AC42" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AD42" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA42" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>3.24</v>
-      </c>
       <c r="BB42" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10260,130 +10260,130 @@
         <v>1.75</v>
       </c>
       <c r="Q50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W50" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD50" t="n">
         <v>3.5</v>
       </c>
-      <c r="R50" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>0</v>
-      </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,130 +10454,130 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>6.03</v>
+        <v>3.5</v>
       </c>
       <c r="S51" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="T51" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="V51" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W51" t="n">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="X51" t="n">
         <v>2.69</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="Z51" t="n">
-        <v>5.75</v>
+        <v>6.65</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AI51" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AN51" t="n">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB51" t="n">
         <v>1.19</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1.22</v>
       </c>
       <c r="BC51" t="n">
         <v>2.05</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BF51" t="n">
         <v>1.18</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,130 +10651,130 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>4.16</v>
       </c>
       <c r="R52" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="S52" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T52" t="n">
         <v>2.3</v>
       </c>
-      <c r="T52" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U52" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="V52" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W52" t="n">
-        <v>2.89</v>
+        <v>3.22</v>
       </c>
       <c r="X52" t="n">
         <v>2.69</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AB52" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.55</v>
+        <v>3.82</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI52" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AL52" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB52" t="n">
         <v>1.22</v>
       </c>
-      <c r="AQ52" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS52" t="n">
+      <c r="BC52" t="n">
         <v>2.05</v>
       </c>
-      <c r="AT52" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BD52" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BF52" t="n">
         <v>1.18</v>
@@ -10848,28 +10848,28 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="Q53" t="n">
         <v>3.19</v>
       </c>
       <c r="R53" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="S53" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="T53" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U53" t="n">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="V53" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W53" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="X53" t="n">
         <v>2.94</v>
@@ -10884,7 +10884,7 @@
         <v>1.04</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AC53" t="n">
         <v>1.33</v>
@@ -10893,22 +10893,22 @@
         <v>3</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG53" t="n">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AI53" t="n">
         <v>7.5</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK53" t="n">
         <v>1.8</v>
@@ -10917,10 +10917,10 @@
         <v>1.91</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10956,22 +10956,22 @@
         <v>1.35</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="BA53" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="BB53" t="n">
         <v>1.29</v>
       </c>
       <c r="BC53" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="BD53" t="n">
         <v>3.3</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BF53" t="n">
         <v>1.14</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,124 +11045,124 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R54" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="S54" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="T54" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U54" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="V54" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W54" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="X54" t="n">
-        <v>2.85</v>
+        <v>3.11</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB54" t="n">
         <v>1.06</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AD54" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AE54" t="n">
         <v>2.08</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="AT54" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="AU54" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="BA54" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="BD54" t="n">
         <v>3.3</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>5.02</v>
+        <v>3.2</v>
       </c>
       <c r="S55" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="T55" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U55" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="V55" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W55" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="X55" t="n">
-        <v>3.09</v>
+        <v>3.32</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z55" t="n">
         <v>7</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AB55" t="n">
         <v>1.06</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI55" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL55" t="n">
         <v>1.85</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AN55" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AQ55" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB55" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC55" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11636,40 +11636,40 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.35</v>
+        <v>3.11</v>
       </c>
       <c r="R57" t="n">
-        <v>2.44</v>
+        <v>2.61</v>
       </c>
       <c r="S57" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T57" t="n">
         <v>2.1</v>
       </c>
       <c r="U57" t="n">
-        <v>2.95</v>
+        <v>3.29</v>
       </c>
       <c r="V57" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W57" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="X57" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z57" t="n">
         <v>7.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB57" t="n">
         <v>1.06</v>
@@ -11687,7 +11687,7 @@
         <v>1.73</v>
       </c>
       <c r="AG57" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AH57" t="n">
         <v>1.25</v>
@@ -11705,10 +11705,10 @@
         <v>1.95</v>
       </c>
       <c r="AM57" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AN57" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
@@ -11833,22 +11833,22 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R58" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="S58" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="T58" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="U58" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="V58" t="n">
         <v>1.43</v>
@@ -11869,31 +11869,31 @@
         <v>1.07</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="AH58" t="n">
         <v>1.39</v>
       </c>
       <c r="AI58" t="n">
-        <v>5.63</v>
+        <v>4.95</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK58" t="n">
         <v>1.73</v>
@@ -11902,61 +11902,61 @@
         <v>2</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AN58" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
       </c>
       <c r="AP58" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB58" t="n">
         <v>1.2</v>
       </c>
-      <c r="AQ58" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB58" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC58" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BD58" t="n">
         <v>3.8</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BF58" t="n">
         <v>1.18</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
-        <v>2.32</v>
+        <v>3.6</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2.54</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.95</v>
+        <v>4.69</v>
       </c>
       <c r="V2" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="X2" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AK2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL2" t="n">
         <v>1.95</v>
       </c>
-      <c r="AL2" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AM2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -882,25 +882,25 @@
         <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AR2" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.97</v>
+        <v>5.04</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AX2" t="n">
         <v>1.24</v>
@@ -909,25 +909,25 @@
         <v>1.09</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.23</v>
+        <v>1.51</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.82</v>
+        <v>2.43</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,73 +1195,73 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE4" t="n">
         <v>2.15</v>
       </c>
-      <c r="U4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.24</v>
+        <v>3.9</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
         <v>1.36</v>
@@ -1273,55 +1273,55 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.04</v>
+        <v>3.42</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.6</v>
+        <v>3.79</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.74</v>
+        <v>5.82</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.87</v>
+        <v>2.19</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="Q5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X5" t="n">
         <v>3.25</v>
       </c>
-      <c r="R5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.96</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.05</v>
       </c>
-      <c r="AC5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AK5" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="AL5" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL5" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AM5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1473,25 +1473,25 @@
         <v>1.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.04</v>
+        <v>4.97</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AX5" t="n">
         <v>1.24</v>
@@ -1500,25 +1500,25 @@
         <v>1.09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.51</v>
+        <v>2.23</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.43</v>
+        <v>1.82</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>3.7</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>1.5</v>
       </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>3.7</v>
       </c>
       <c r="S17" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5138,10 +5138,10 @@
         <v>1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="S24" t="n">
         <v>2.02</v>
@@ -5153,10 +5153,10 @@
         <v>5.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="X24" t="n">
         <v>2.38</v>
@@ -5165,16 +5165,16 @@
         <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AB24" t="n">
         <v>1.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AD24" t="n">
         <v>3.95</v>
@@ -5189,19 +5189,19 @@
         <v>2.65</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK24" t="n">
         <v>1.7</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AM24" t="n">
         <v>1.2</v>
@@ -5213,55 +5213,55 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.65</v>
+        <v>3.16</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="AW24" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AZ24" t="n">
         <v>1.28</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.8</v>
+        <v>4.84</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
         <v>1.85</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE24" t="n">
         <v>1.85</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5347,7 +5347,7 @@
         <v>2.45</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V25" t="n">
         <v>1.19</v>
@@ -5383,7 +5383,7 @@
         <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH25" t="n">
         <v>1.64</v>
@@ -5446,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BC25" t="n">
         <v>1.67</v>
@@ -5458,7 +5458,7 @@
         <v>2.05</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="Q26" t="n">
         <v>3.4</v>
@@ -5547,7 +5547,7 @@
         <v>2.98</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
         <v>2.9</v>
@@ -5577,7 +5577,7 @@
         <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
         <v>2.9</v>
@@ -5592,16 +5592,16 @@
         <v>1.13</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AM26" t="n">
         <v>1.33</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
         <v>3.65</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S30" t="n">
-        <v>1.59</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="W30" t="n">
-        <v>4.3</v>
+        <v>3.07</v>
       </c>
       <c r="X30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL30" t="n">
         <v>2.04</v>
       </c>
-      <c r="Y30" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AM30" t="n">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.72</v>
+        <v>1.5</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AX30" t="n">
         <v>1.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.05</v>
+        <v>1.89</v>
       </c>
       <c r="BA30" t="n">
-        <v>9.9</v>
+        <v>2.02</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6523,124 +6523,124 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6711,19 +6711,19 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="R32" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="S32" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T32" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="U32" t="n">
         <v>3.25</v>
@@ -6741,13 +6741,13 @@
         <v>1.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC32" t="n">
         <v>1.36</v>
@@ -6756,10 +6756,10 @@
         <v>2.85</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG32" t="n">
         <v>3.8</v>
@@ -6795,10 +6795,10 @@
         <v>1.71</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AT32" t="n">
         <v>3.7</v>
@@ -6807,13 +6807,13 @@
         <v>2.63</v>
       </c>
       <c r="AV32" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AY32" t="n">
         <v>1.23</v>
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R33" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="S33" t="n">
         <v>3.05</v>
@@ -6938,13 +6938,13 @@
         <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AC33" t="n">
         <v>1.43</v>
@@ -6971,7 +6971,7 @@
         <v>1.06</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AL33" t="n">
         <v>1.76</v>
@@ -7022,7 +7022,7 @@
         <v>2.23</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BC33" t="n">
         <v>2.55</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7186,52 +7186,52 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7514,7 +7514,7 @@
         <v>2.62</v>
       </c>
       <c r="U36" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V36" t="n">
         <v>1.25</v>
@@ -7547,7 +7547,7 @@
         <v>1.46</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AG36" t="n">
         <v>2.2</v>
@@ -7568,10 +7568,10 @@
         <v>1.85</v>
       </c>
       <c r="AM36" t="n">
-        <v>3.5</v>
+        <v>1.15</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7616,16 +7616,16 @@
         <v>1.17</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="BD36" t="n">
         <v>4.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.15</v>
+        <v>3.75</v>
       </c>
       <c r="R39" t="n">
-        <v>8.6</v>
+        <v>2.57</v>
       </c>
       <c r="S39" t="n">
-        <v>1.68</v>
+        <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="U39" t="n">
-        <v>7.1</v>
+        <v>3.02</v>
       </c>
       <c r="V39" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="W39" t="n">
-        <v>4.65</v>
+        <v>3.36</v>
       </c>
       <c r="X39" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AD39" t="n">
-        <v>7</v>
+        <v>3.84</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.33</v>
+        <v>1.76</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.72</v>
+        <v>5.5</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="AK39" t="n">
         <v>1.6</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AN39" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.82</v>
+        <v>1.43</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AZ39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB39" t="n">
         <v>1.2</v>
       </c>
-      <c r="BA39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BC39" t="n">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="BD39" t="n">
-        <v>7.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="R40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="S40" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W40" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN40" t="n">
         <v>3.7</v>
       </c>
-      <c r="R40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U40" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W40" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF40" t="n">
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR40" t="n">
         <v>1.82</v>
       </c>
-      <c r="AG40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
+      <c r="AS40" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY40" t="n">
         <v>1.33</v>
       </c>
-      <c r="AQ40" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AZ40" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="BA40" t="n">
-        <v>3.24</v>
+        <v>5.2</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.4</v>
+        <v>7.9</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R42" t="n">
-        <v>2.57</v>
+        <v>4.5</v>
       </c>
       <c r="S42" t="n">
-        <v>3.1</v>
+        <v>2.29</v>
       </c>
       <c r="T42" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U42" t="n">
-        <v>3.02</v>
+        <v>4.75</v>
       </c>
       <c r="V42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC42" t="n">
         <v>1.3</v>
       </c>
-      <c r="W42" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AD42" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AI42" t="n">
-        <v>5.5</v>
+        <v>6.65</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK42" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE42" t="n">
         <v>1.6</v>
       </c>
-      <c r="AL42" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BF42" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.9</v>
+        <v>2.21</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.11</v>
+        <v>3.35</v>
       </c>
       <c r="R57" t="n">
-        <v>2.61</v>
+        <v>3.25</v>
       </c>
       <c r="S57" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="T57" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="U57" t="n">
-        <v>3.29</v>
+        <v>3.94</v>
       </c>
       <c r="V57" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W57" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X57" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y57" t="n">
         <v>1.44</v>
       </c>
-      <c r="W57" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y57" t="n">
+      <c r="Z57" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ57" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z57" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AR57" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AS57" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="AU57" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AV57" t="n">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AZ57" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="BA57" t="n">
-        <v>1.94</v>
+        <v>2.8</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC57" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,133 +11833,133 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.21</v>
+        <v>2.9</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.35</v>
+        <v>3.11</v>
       </c>
       <c r="R58" t="n">
-        <v>3.25</v>
+        <v>2.61</v>
       </c>
       <c r="S58" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="T58" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="U58" t="n">
-        <v>3.94</v>
+        <v>3.29</v>
       </c>
       <c r="V58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W58" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN58" t="n">
         <v>1.43</v>
       </c>
-      <c r="W58" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X58" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC58" t="n">
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BB58" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD58" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW58" t="n">
+      <c r="BC58" t="n">
         <v>2.2</v>
       </c>
-      <c r="AX58" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB58" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC58" t="n">
-        <v>1.96</v>
-      </c>
       <c r="BD58" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X2" t="n">
         <v>3.25</v>
       </c>
-      <c r="R2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U2" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.96</v>
-      </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.05</v>
       </c>
-      <c r="AC2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AK2" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL2" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AM2" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -882,25 +882,25 @@
         <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.04</v>
+        <v>4.97</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AX2" t="n">
         <v>1.24</v>
@@ -909,25 +909,25 @@
         <v>1.09</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.51</v>
+        <v>2.23</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.43</v>
+        <v>1.82</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>2.93</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U4" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="X4" t="n">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.06</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
         <v>1.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,22 +1276,22 @@
         <v>1.59</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.82</v>
+        <v>5.77</v>
       </c>
       <c r="AU4" t="n">
         <v>2.19</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AW4" t="n">
         <v>1.39</v>
@@ -1303,25 +1303,25 @@
         <v>1.05</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.01</v>
+        <v>1.71</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W5" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="X5" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.87</v>
       </c>
       <c r="AR5" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.34</v>
+        <v>3.79</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.97</v>
+        <v>5.82</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S6" t="n">
         <v>2.54</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.2</v>
       </c>
       <c r="T6" t="n">
         <v>2.05</v>
       </c>
       <c r="U6" t="n">
-        <v>3.2</v>
+        <v>4.69</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AU6" t="n">
         <v>2.36</v>
       </c>
-      <c r="X6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AV6" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.9</v>
+        <v>2.43</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1986,31 +1986,31 @@
         <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="R8" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
         <v>2.14</v>
       </c>
       <c r="U8" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="X8" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
         <v>9</v>
@@ -2019,7 +2019,7 @@
         <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AC8" t="n">
         <v>1.32</v>
@@ -2037,7 +2037,7 @@
         <v>4.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AI8" t="n">
         <v>8.5</v>
@@ -2064,52 +2064,52 @@
         <v>1.57</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AS8" t="n">
         <v>3.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="AU8" t="n">
         <v>2.23</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AX8" t="n">
         <v>1.26</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BC8" t="n">
         <v>2.45</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="BE8" t="n">
         <v>1.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -3559,28 +3559,28 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S16" t="n">
         <v>5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.9</v>
       </c>
       <c r="T16" t="n">
         <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W16" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="X16" t="n">
         <v>2.39</v>
@@ -3589,7 +3589,7 @@
         <v>1.51</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA16" t="n">
         <v>1.09</v>
@@ -3607,7 +3607,7 @@
         <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
         <v>2.48</v>
@@ -3616,10 +3616,10 @@
         <v>1.44</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK16" t="n">
         <v>1.65</v>
@@ -3631,7 +3631,7 @@
         <v>1.18</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>1.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AS16" t="n">
         <v>2.33</v>
@@ -3676,13 +3676,13 @@
         <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BD16" t="n">
         <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BF16" t="n">
         <v>1.22</v>
@@ -3953,19 +3953,19 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="R18" t="n">
-        <v>5.95</v>
+        <v>5.4</v>
       </c>
       <c r="S18" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="T18" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U18" t="n">
         <v>6</v>
@@ -3977,16 +3977,16 @@
         <v>3.15</v>
       </c>
       <c r="X18" t="n">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="Y18" t="n">
         <v>1.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB18" t="n">
         <v>1.03</v>
@@ -4004,7 +4004,7 @@
         <v>2.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="AH18" t="n">
         <v>1.48</v>
@@ -4013,10 +4013,10 @@
         <v>4.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AL18" t="n">
         <v>1.95</v>
@@ -4025,7 +4025,7 @@
         <v>1.2</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>1.25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.72</v>
+        <v>2.44</v>
       </c>
       <c r="AS18" t="n">
         <v>2.12</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AX18" t="n">
         <v>1.62</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4938,16 +4938,16 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="R23" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="S23" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="T23" t="n">
         <v>2.7</v>
@@ -4962,31 +4962,31 @@
         <v>4.2</v>
       </c>
       <c r="X23" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AB23" t="n">
         <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AG23" t="n">
         <v>2</v>
@@ -4998,7 +4998,7 @@
         <v>3.25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK23" t="n">
         <v>1.49</v>
@@ -5007,37 +5007,37 @@
         <v>2.59</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AT23" t="n">
         <v>2.05</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AX23" t="n">
         <v>2.12</v>
@@ -5046,25 +5046,25 @@
         <v>1.7</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BD23" t="n">
         <v>5.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.74</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="R25" t="n">
-        <v>2.09</v>
+        <v>3.37</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF25" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>2.74</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="R27" t="n">
-        <v>3.37</v>
+        <v>2.09</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.88</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U30" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>3.07</v>
+        <v>4.3</v>
       </c>
       <c r="X30" t="n">
-        <v>2.73</v>
+        <v>2.04</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z30" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC30" t="n">
+      <c r="AF30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK30" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.5</v>
+        <v>3.72</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AX30" t="n">
         <v>1.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.89</v>
+        <v>1.05</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.02</v>
+        <v>9.9</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6523,124 +6523,124 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="R33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X33" t="n">
         <v>3</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.25</v>
-      </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="AG33" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AI33" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AM33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN33" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.45</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -6992,49 +6992,49 @@
         <v>1.71</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AU33" t="n">
         <v>2.63</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="BB33" t="n">
         <v>1.33</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7383,52 +7383,52 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU35" t="n">
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R37" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="S37" t="n">
         <v>2.35</v>
@@ -7711,13 +7711,13 @@
         <v>2.33</v>
       </c>
       <c r="U37" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="V37" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W37" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X37" t="n">
         <v>2.38</v>
@@ -7732,7 +7732,7 @@
         <v>1.08</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC37" t="n">
         <v>1.22</v>
@@ -7741,10 +7741,10 @@
         <v>4</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
         <v>2.6</v>
@@ -7753,16 +7753,16 @@
         <v>1.39</v>
       </c>
       <c r="AI37" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AJ37" t="n">
         <v>1.12</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="AM37" t="n">
         <v>1.23</v>
@@ -7810,19 +7810,19 @@
         <v>3.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC37" t="n">
         <v>1.92</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7893,22 +7893,22 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Q38" t="n">
         <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="S38" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="T38" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="U38" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="V38" t="n">
         <v>1.38</v>
@@ -7950,7 +7950,7 @@
         <v>1.3</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.7</v>
+        <v>6.21</v>
       </c>
       <c r="AJ38" t="n">
         <v>1.11</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U39" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z39" t="n">
         <v>3.75</v>
       </c>
-      <c r="R39" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V39" t="n">
+      <c r="AA39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE39" t="n">
         <v>1.3</v>
       </c>
-      <c r="W39" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA39" t="n">
+      <c r="AF39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM39" t="n">
         <v>1.12</v>
       </c>
-      <c r="AB39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AN39" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB39" t="n">
         <v>1.13</v>
       </c>
-      <c r="AQ39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC39" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,76 +8287,76 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.15</v>
+        <v>5.75</v>
       </c>
       <c r="R40" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="S40" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T40" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U40" t="n">
-        <v>7.1</v>
+        <v>6.38</v>
       </c>
       <c r="V40" t="n">
         <v>1.17</v>
       </c>
       <c r="W40" t="n">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="X40" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AB40" t="n">
         <v>1.01</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AD40" t="n">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF40" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AI40" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AN40" t="n">
         <v>3.7</v>
@@ -8365,49 +8365,49 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.95</v>
+        <v>1.91</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.38</v>
+        <v>3.45</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="BD40" t="n">
-        <v>7.9</v>
+        <v>5.75</v>
       </c>
       <c r="BE40" t="n">
         <v>2.25</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.5</v>
+        <v>3.76</v>
       </c>
       <c r="R41" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="S41" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U41" t="n">
-        <v>6.57</v>
+        <v>2.99</v>
       </c>
       <c r="V41" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="W41" t="n">
-        <v>4.55</v>
+        <v>3.42</v>
       </c>
       <c r="X41" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AD41" t="n">
-        <v>6.25</v>
+        <v>4</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="AF41" t="n">
-        <v>3.19</v>
+        <v>2.1</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.88</v>
+        <v>2.76</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="AI41" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="AN41" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AT41" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC41" t="n">
         <v>2.02</v>
       </c>
-      <c r="AU41" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BD41" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8681,19 +8681,19 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R42" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="S42" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="T42" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U42" t="n">
         <v>4.75</v>
@@ -8738,7 +8738,7 @@
         <v>1.26</v>
       </c>
       <c r="AI42" t="n">
-        <v>6.65</v>
+        <v>5.2</v>
       </c>
       <c r="AJ42" t="n">
         <v>1.1</v>
@@ -8753,7 +8753,7 @@
         <v>1.29</v>
       </c>
       <c r="AN42" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8762,13 +8762,13 @@
         <v>1.33</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="AT42" t="n">
         <v>3.74</v>
@@ -8780,25 +8780,25 @@
         <v>2.12</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AZ42" t="n">
         <v>1.42</v>
       </c>
       <c r="BA42" t="n">
-        <v>3.24</v>
+        <v>2.83</v>
       </c>
       <c r="BB42" t="n">
         <v>1.25</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BD42" t="n">
         <v>3.4</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,130 +10454,130 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>4.16</v>
       </c>
       <c r="R51" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="S51" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="T51" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U51" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="V51" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W51" t="n">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="X51" t="n">
         <v>2.69</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="AH51" t="n">
         <v>1.33</v>
       </c>
       <c r="AI51" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AL51" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB51" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1.19</v>
       </c>
       <c r="BC51" t="n">
         <v>2.05</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BF51" t="n">
         <v>1.18</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,130 +10651,130 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.16</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="S52" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="T52" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="V52" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W52" t="n">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="X52" t="n">
         <v>2.69</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z52" t="n">
-        <v>5.75</v>
+        <v>6.65</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AH52" t="n">
         <v>1.33</v>
       </c>
       <c r="AI52" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AM52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="n">
+      <c r="AQ52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB52" t="n">
         <v>1.19</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>1.22</v>
       </c>
       <c r="BC52" t="n">
         <v>2.05</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BF52" t="n">
         <v>1.18</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.21</v>
+        <v>2.9</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.35</v>
+        <v>3.11</v>
       </c>
       <c r="R57" t="n">
-        <v>3.25</v>
+        <v>2.61</v>
       </c>
       <c r="S57" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="T57" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="U57" t="n">
-        <v>3.94</v>
+        <v>3.29</v>
       </c>
       <c r="V57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W57" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X57" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN57" t="n">
         <v>1.43</v>
       </c>
-      <c r="W57" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC57" t="n">
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BB57" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD57" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW57" t="n">
+      <c r="BC57" t="n">
         <v>2.2</v>
       </c>
-      <c r="AX57" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>1.96</v>
-      </c>
       <c r="BD57" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,133 +11833,133 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.9</v>
+        <v>2.21</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.11</v>
+        <v>3.35</v>
       </c>
       <c r="R58" t="n">
-        <v>2.61</v>
+        <v>3.25</v>
       </c>
       <c r="S58" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="T58" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="U58" t="n">
-        <v>3.29</v>
+        <v>3.94</v>
       </c>
       <c r="V58" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W58" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y58" t="n">
         <v>1.44</v>
       </c>
-      <c r="W58" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X58" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y58" t="n">
+      <c r="Z58" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ58" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z58" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AR58" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AS58" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="AT58" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="AU58" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AV58" t="n">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AZ58" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.94</v>
+        <v>2.8</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC58" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="BD58" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R2" t="n">
         <v>2.32</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="X2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AG2" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.87</v>
       </c>
       <c r="AR2" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="AS2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD2" t="n">
         <v>3.34</v>
       </c>
-      <c r="AT2" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3</v>
-      </c>
       <c r="BE2" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
         <v>2.95</v>
@@ -1213,7 +1213,7 @@
         <v>3.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
         <v>2.36</v>
@@ -1303,7 +1303,7 @@
         <v>1.05</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="BA4" t="n">
         <v>2.9</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,73 +1392,73 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="V5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="X5" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.9</v>
+        <v>3.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AI5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AM5" t="n">
         <v>1.36</v>
@@ -1470,55 +1470,55 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.42</v>
+        <v>2.04</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.79</v>
+        <v>2.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.82</v>
+        <v>3.74</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.19</v>
+        <v>2.87</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="AW5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX5" t="n">
         <v>1.39</v>
       </c>
-      <c r="AX5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AY5" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1592,19 +1592,19 @@
         <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="S6" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="T6" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="U6" t="n">
-        <v>4.69</v>
+        <v>3.8</v>
       </c>
       <c r="V6" t="n">
         <v>1.39</v>
@@ -1613,7 +1613,7 @@
         <v>2.73</v>
       </c>
       <c r="X6" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="Y6" t="n">
         <v>1.4</v>
@@ -1628,10 +1628,10 @@
         <v>1.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AE6" t="n">
         <v>1.95</v>
@@ -1640,10 +1640,10 @@
         <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AI6" t="n">
         <v>6.5</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.16</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.64</v>
+        <v>3.7</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="R17" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,37 +3953,37 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.53</v>
+        <v>4.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.33</v>
+        <v>4.16</v>
       </c>
       <c r="R18" t="n">
-        <v>5.4</v>
+        <v>1.64</v>
       </c>
       <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U18" t="n">
         <v>2.05</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6</v>
-      </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="X18" t="n">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="Y18" t="n">
         <v>1.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="AA18" t="n">
         <v>1.09</v>
@@ -3998,88 +3998,88 @@
         <v>4.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
         <v>2.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AJ18" t="n">
         <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AL18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR18" t="n">
         <v>1.95</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AS18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.2</v>
       </c>
-      <c r="AN18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.16</v>
-      </c>
       <c r="BC18" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>2.61</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>3.37</v>
+        <v>2.46</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.61</v>
+        <v>2.74</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="R26" t="n">
-        <v>2.46</v>
+        <v>2.09</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>2.98</v>
+        <v>2.59</v>
       </c>
       <c r="V26" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W26" t="n">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="X26" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.85</v>
+        <v>4.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AI26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BD26" t="n">
         <v>5</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE26" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.74</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="R27" t="n">
-        <v>2.09</v>
+        <v>3.37</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF27" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG27" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S30" t="n">
-        <v>1.59</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="W30" t="n">
-        <v>4.3</v>
+        <v>3.07</v>
       </c>
       <c r="X30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL30" t="n">
         <v>2.04</v>
       </c>
-      <c r="Y30" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AM30" t="n">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.72</v>
+        <v>1.5</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AX30" t="n">
         <v>1.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.05</v>
+        <v>1.89</v>
       </c>
       <c r="BA30" t="n">
-        <v>9.9</v>
+        <v>2.02</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T35" t="n">
         <v>2.88</v>
       </c>
-      <c r="T35" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U35" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="V35" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="W35" t="n">
-        <v>3.07</v>
+        <v>4.3</v>
       </c>
       <c r="X35" t="n">
-        <v>2.73</v>
+        <v>2.04</v>
       </c>
       <c r="Y35" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE35" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z35" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC35" t="n">
+      <c r="AF35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD35" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK35" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.5</v>
+        <v>3.72</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AX35" t="n">
         <v>1.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.89</v>
+        <v>1.05</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.02</v>
+        <v>9.9</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="S37" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="T37" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="U37" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="V37" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W37" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="X37" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC37" t="n">
         <v>1.22</v>
       </c>
       <c r="AD37" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AI37" t="n">
-        <v>4.65</v>
+        <v>6.21</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE37" t="n">
         <v>1.65</v>
       </c>
-      <c r="AL37" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
+      <c r="BF37" t="n">
         <v>1.17</v>
       </c>
-      <c r="AQ37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R38" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="S38" t="n">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="T38" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="U38" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="V38" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="W38" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="X38" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC38" t="n">
         <v>1.22</v>
       </c>
       <c r="AD38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA38" t="n">
         <v>3.4</v>
       </c>
-      <c r="AE38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW38" t="n">
+      <c r="BB38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE38" t="n">
         <v>1.8</v>
       </c>
-      <c r="AX38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BF38" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46099.69791666666</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="S54" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="T54" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U54" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="V54" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W54" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="X54" t="n">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z54" t="n">
         <v>7</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AB54" t="n">
         <v>1.06</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI54" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK54" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AN54" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB54" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR54" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC54" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R55" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T55" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.05</v>
-      </c>
       <c r="U55" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="V55" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W55" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="X55" t="n">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z55" t="n">
         <v>7</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB55" t="n">
         <v>1.06</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG55" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI55" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AN55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE55" t="n">
         <v>1.57</v>
       </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF55" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.9</v>
+        <v>2.21</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.11</v>
+        <v>3.35</v>
       </c>
       <c r="R57" t="n">
-        <v>2.61</v>
+        <v>3.25</v>
       </c>
       <c r="S57" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="T57" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="U57" t="n">
-        <v>3.29</v>
+        <v>3.94</v>
       </c>
       <c r="V57" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W57" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X57" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y57" t="n">
         <v>1.44</v>
       </c>
-      <c r="W57" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y57" t="n">
+      <c r="Z57" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ57" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z57" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AR57" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AS57" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="AU57" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AV57" t="n">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AZ57" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="BA57" t="n">
-        <v>1.94</v>
+        <v>2.8</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC57" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,133 +11833,133 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.21</v>
+        <v>2.9</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.35</v>
+        <v>3.11</v>
       </c>
       <c r="R58" t="n">
-        <v>3.25</v>
+        <v>2.61</v>
       </c>
       <c r="S58" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="T58" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="U58" t="n">
-        <v>3.94</v>
+        <v>3.29</v>
       </c>
       <c r="V58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W58" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN58" t="n">
         <v>1.43</v>
       </c>
-      <c r="W58" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X58" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC58" t="n">
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BB58" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD58" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW58" t="n">
+      <c r="BC58" t="n">
         <v>2.2</v>
       </c>
-      <c r="AX58" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB58" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC58" t="n">
-        <v>1.96</v>
-      </c>
       <c r="BD58" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,73 +801,73 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="X2" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB2" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB2" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC2" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.9</v>
+        <v>3.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AI2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.06</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
         <v>1.36</v>
@@ -879,55 +879,55 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.42</v>
+        <v>2.04</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.79</v>
+        <v>2.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.82</v>
+        <v>3.74</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.32</v>
+        <v>2.87</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AW2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX2" t="n">
         <v>1.39</v>
       </c>
-      <c r="AX2" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AY2" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC3" t="n">
         <v>2.2</v>
       </c>
-      <c r="S3" t="n">
-        <v>4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BD3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.95</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.2</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="X4" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AK4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR4" t="n">
         <v>2.3</v>
       </c>
-      <c r="AF4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH4" t="n">
+      <c r="AS4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX4" t="n">
         <v>1.2</v>
       </c>
-      <c r="AI4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AY4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.9</v>
+        <v>1.76</v>
       </c>
       <c r="BB4" t="n">
         <v>1.33</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S5" t="n">
         <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U5" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>2.59</v>
+        <v>2.36</v>
       </c>
       <c r="X5" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.44</v>
+        <v>2.75</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AL5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AM5" t="n">
         <v>1.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.04</v>
+        <v>3.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.6</v>
+        <v>3.76</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.74</v>
+        <v>5.77</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.87</v>
+        <v>2.19</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>2.67</v>
       </c>
       <c r="Q6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S6" t="n">
         <v>3.3</v>
       </c>
-      <c r="R6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.51</v>
-      </c>
       <c r="T6" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="X6" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
         <v>1.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL6" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG6" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AM6" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.38</v>
+        <v>3.79</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.04</v>
+        <v>5.82</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AV6" t="n">
         <v>1.82</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.51</v>
+        <v>2.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1983,25 +1983,25 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q8" t="n">
         <v>3.28</v>
       </c>
       <c r="R8" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="T8" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="U8" t="n">
-        <v>3.75</v>
+        <v>4.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
         <v>2.5</v>
@@ -2013,7 +2013,7 @@
         <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AA8" t="n">
         <v>1.01</v>
@@ -2040,7 +2040,7 @@
         <v>1.2</v>
       </c>
       <c r="AI8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.06</v>
@@ -2052,10 +2052,10 @@
         <v>1.8</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AR8" t="n">
         <v>2.88</v>
@@ -2073,28 +2073,28 @@
         <v>3.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.26</v>
+        <v>4.75</v>
       </c>
       <c r="AU8" t="n">
         <v>2.23</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AX8" t="n">
         <v>1.26</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="BB8" t="n">
         <v>1.33</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3762,10 +3762,10 @@
         <v>4.33</v>
       </c>
       <c r="R17" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="S17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="T17" t="n">
         <v>2.38</v>
@@ -3783,7 +3783,7 @@
         <v>2.49</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
         <v>5.3</v>
@@ -3834,40 +3834,40 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AR17" t="n">
         <v>2.44</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.12</v>
+        <v>2.74</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.54</v>
+        <v>3.84</v>
       </c>
       <c r="BB17" t="n">
         <v>1.16</v>
@@ -3953,16 +3953,16 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="T18" t="n">
         <v>2.4</v>
@@ -3971,10 +3971,10 @@
         <v>2.05</v>
       </c>
       <c r="V18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="X18" t="n">
         <v>2.39</v>
@@ -3983,10 +3983,10 @@
         <v>1.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AB18" t="n">
         <v>1.03</v>
@@ -3995,7 +3995,7 @@
         <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AE18" t="n">
         <v>1.57</v>
@@ -4007,25 +4007,25 @@
         <v>2.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AM18" t="n">
         <v>1.18</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
         <v>1.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AS18" t="n">
         <v>2.33</v>
@@ -4052,7 +4052,7 @@
         <v>2.35</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AX18" t="n">
         <v>1.52</v>
@@ -4061,7 +4061,7 @@
         <v>1.32</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="BA18" t="n">
         <v>1.46</v>
@@ -4070,16 +4070,16 @@
         <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="BD18" t="n">
         <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.68</v>
+        <v>3.48</v>
       </c>
       <c r="Q20" t="n">
         <v>2.93</v>
@@ -4356,10 +4356,10 @@
         <v>2.26</v>
       </c>
       <c r="S20" t="n">
-        <v>4.05</v>
+        <v>4.66</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U20" t="n">
         <v>2.9</v>
@@ -4371,10 +4371,10 @@
         <v>2.17</v>
       </c>
       <c r="X20" t="n">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
         <v>8.5</v>
@@ -4389,7 +4389,7 @@
         <v>1.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AE20" t="n">
         <v>2.75</v>
@@ -4401,7 +4401,7 @@
         <v>5.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
         <v>9.5</v>
@@ -4416,10 +4416,10 @@
         <v>1.62</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
         <v>1.69</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AS20" t="n">
         <v>3</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.61</v>
+        <v>2.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="R25" t="n">
-        <v>2.46</v>
+        <v>2.09</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="U25" t="n">
-        <v>2.98</v>
+        <v>2.59</v>
       </c>
       <c r="V25" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W25" t="n">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="X25" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.85</v>
+        <v>4.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AI25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BD25" t="n">
         <v>5</v>
       </c>
-      <c r="AJ25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE25" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>2.09</v>
+        <v>2.46</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>2.59</v>
+        <v>2.98</v>
       </c>
       <c r="V26" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="X26" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.7</v>
+        <v>5.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AD26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI26" t="n">
         <v>5</v>
       </c>
-      <c r="AE26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.22</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="S30" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="T30" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="U30" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="V30" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="W30" t="n">
-        <v>3.07</v>
+        <v>2.31</v>
       </c>
       <c r="X30" t="n">
-        <v>2.73</v>
+        <v>3.32</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC30" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z30" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>1.05</v>
       </c>
-      <c r="AC30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE30" t="n">
+      <c r="AK30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN30" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ30" t="n">
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF30" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG32" t="n">
         <v>3.1</v>
       </c>
-      <c r="R32" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U32" t="n">
-        <v>5</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AH32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF32" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7311,34 +7311,34 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="U35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V35" t="n">
         <v>1.18</v>
       </c>
       <c r="W35" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="X35" t="n">
         <v>2.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
         <v>1.09</v>
@@ -7350,13 +7350,13 @@
         <v>1.4</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AI35" t="n">
         <v>3.14</v>
@@ -7371,10 +7371,10 @@
         <v>1.86</v>
       </c>
       <c r="AM35" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AN35" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7422,13 +7422,13 @@
         <v>1.62</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE35" t="n">
         <v>2.15</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7508,13 +7508,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="T36" t="n">
         <v>2.62</v>
       </c>
       <c r="U36" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V36" t="n">
         <v>1.25</v>
@@ -7523,7 +7523,7 @@
         <v>3.7</v>
       </c>
       <c r="X36" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Y36" t="n">
         <v>1.64</v>
@@ -7538,7 +7538,7 @@
         <v>1.02</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AD36" t="n">
         <v>5</v>
@@ -7547,13 +7547,13 @@
         <v>1.46</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AG36" t="n">
         <v>2.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AI36" t="n">
         <v>3.5</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="R39" t="n">
-        <v>8.4</v>
+        <v>4.1</v>
       </c>
       <c r="S39" t="n">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="T39" t="n">
-        <v>2.95</v>
+        <v>2.13</v>
       </c>
       <c r="U39" t="n">
-        <v>6.95</v>
+        <v>4.75</v>
       </c>
       <c r="V39" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="W39" t="n">
-        <v>4.65</v>
+        <v>2.81</v>
       </c>
       <c r="X39" t="n">
-        <v>1.8</v>
+        <v>2.77</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="AF39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BD39" t="n">
         <v>3.4</v>
       </c>
-      <c r="AG39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>5.75</v>
-      </c>
       <c r="BE39" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,124 +8287,124 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.75</v>
+        <v>6.2</v>
       </c>
       <c r="R40" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="S40" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="T40" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="U40" t="n">
-        <v>6.38</v>
+        <v>6.95</v>
       </c>
       <c r="V40" t="n">
         <v>1.17</v>
       </c>
       <c r="W40" t="n">
-        <v>4.25</v>
+        <v>4.65</v>
       </c>
       <c r="X40" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AB40" t="n">
         <v>1.01</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AD40" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF40" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AI40" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AM40" t="n">
         <v>1.12</v>
       </c>
       <c r="AN40" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB40" t="n">
         <v>1.13</v>
       </c>
-      <c r="AQ40" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BC40" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BD40" t="n">
         <v>5.75</v>
@@ -8413,7 +8413,7 @@
         <v>2.25</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="R42" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="S42" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="T42" t="n">
-        <v>2.13</v>
+        <v>2.82</v>
       </c>
       <c r="U42" t="n">
-        <v>4.75</v>
+        <v>6.38</v>
       </c>
       <c r="V42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W42" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>1.37</v>
       </c>
-      <c r="W42" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE42" t="n">
+      <c r="AK42" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT42" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF42" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ42" t="n">
+      <c r="AU42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ42" t="n">
         <v>1.1</v>
       </c>
-      <c r="AK42" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.42</v>
-      </c>
       <c r="BA42" t="n">
-        <v>2.83</v>
+        <v>8</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,130 +10454,130 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.16</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="S51" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="T51" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="V51" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W51" t="n">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="X51" t="n">
         <v>2.69</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z51" t="n">
-        <v>5.75</v>
+        <v>6.65</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AH51" t="n">
         <v>1.33</v>
       </c>
       <c r="AI51" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AM51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN51" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
+      <c r="AQ51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB51" t="n">
         <v>1.19</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1.22</v>
       </c>
       <c r="BC51" t="n">
         <v>2.05</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BF51" t="n">
         <v>1.18</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,130 +10651,130 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>4.16</v>
       </c>
       <c r="R52" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="S52" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="T52" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U52" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="V52" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W52" t="n">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="X52" t="n">
         <v>2.69</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG52" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="AH52" t="n">
         <v>1.33</v>
       </c>
       <c r="AI52" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB52" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>1.19</v>
       </c>
       <c r="BC52" t="n">
         <v>2.05</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BF52" t="n">
         <v>1.18</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R54" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T54" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q54" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R54" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.05</v>
-      </c>
       <c r="U54" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="V54" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W54" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="X54" t="n">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z54" t="n">
         <v>7</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB54" t="n">
         <v>1.06</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG54" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AN54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE54" t="n">
         <v>1.57</v>
       </c>
-      <c r="AO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE54" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF54" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="S55" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="T55" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U55" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="V55" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W55" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="X55" t="n">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z55" t="n">
         <v>7</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AB55" t="n">
         <v>1.06</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI55" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK55" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AN55" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AQ55" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB55" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC55" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,73 +801,73 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE2" t="n">
         <v>2.15</v>
       </c>
-      <c r="U2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="AF2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK2" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AM2" t="n">
         <v>1.36</v>
@@ -879,55 +879,55 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.74</v>
+        <v>5.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.87</v>
+        <v>2.32</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="BA2" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
         <v>3.3</v>
@@ -1022,13 +1022,13 @@
         <v>2.73</v>
       </c>
       <c r="X3" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="Y3" t="n">
         <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA3" t="n">
         <v>1.03</v>
@@ -1037,10 +1037,10 @@
         <v>1.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AE3" t="n">
         <v>1.95</v>
@@ -1049,13 +1049,13 @@
         <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.1</v>
@@ -1067,49 +1067,49 @@
         <v>1.95</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.04</v>
+        <v>2.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.04</v>
+        <v>4.33</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="BB3" t="n">
         <v>1.25</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG4" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AH4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.06</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AK4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN4" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD4" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BA4" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.76</v>
       </c>
       <c r="BB4" t="n">
         <v>1.33</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="BD4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="X5" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
         <v>1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AH5" t="n">
         <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.76</v>
+        <v>3.31</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.77</v>
+        <v>4.91</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="BB5" t="n">
         <v>1.33</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,73 +1589,73 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.67</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="X6" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
         <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>8</v>
+        <v>6.05</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AM6" t="n">
         <v>1.36</v>
@@ -1667,55 +1667,55 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.42</v>
+        <v>1.93</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.79</v>
+        <v>2.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.82</v>
+        <v>3.38</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.32</v>
+        <v>3.12</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.82</v>
+        <v>2.26</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.01</v>
+        <v>2.58</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.31</v>
+        <v>1.78</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5135,22 +5135,22 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q24" t="n">
         <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="S24" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="T24" t="n">
         <v>2.4</v>
       </c>
       <c r="U24" t="n">
-        <v>5.1</v>
+        <v>5.75</v>
       </c>
       <c r="V24" t="n">
         <v>1.25</v>
@@ -5159,10 +5159,10 @@
         <v>3.5</v>
       </c>
       <c r="X24" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
         <v>5.05</v>
@@ -5177,82 +5177,82 @@
         <v>1.17</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.2</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AM24" t="n">
         <v>1.2</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AR24" t="n">
         <v>2.19</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.84</v>
+        <v>5.54</v>
       </c>
       <c r="BB24" t="n">
         <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BD24" t="n">
         <v>4.4</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.74</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="R25" t="n">
-        <v>2.09</v>
+        <v>3.37</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF25" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.61</v>
+        <v>2.74</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="R26" t="n">
-        <v>2.46</v>
+        <v>2.09</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>2.98</v>
+        <v>2.59</v>
       </c>
       <c r="V26" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W26" t="n">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="X26" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.85</v>
+        <v>4.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AI26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BD26" t="n">
         <v>5</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE26" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>2.61</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>3.37</v>
+        <v>2.46</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="T29" t="n">
-        <v>1.77</v>
+        <v>2.86</v>
       </c>
       <c r="U29" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="V29" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="W29" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="X29" t="n">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="Z29" t="n">
-        <v>9.300000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="AA29" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.85</v>
+        <v>5.75</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.59</v>
+        <v>2.78</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.8</v>
+        <v>2.06</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.21</v>
+        <v>1.72</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.5</v>
+        <v>3.14</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AK29" t="n">
         <v>1.8</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AM29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY29" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>2.25</v>
+        <v>1.05</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.74</v>
+        <v>9.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R30" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="T30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL30" t="n">
         <v>2.05</v>
       </c>
-      <c r="U30" t="n">
-        <v>5</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH30" t="n">
+      <c r="AM30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF30" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="R32" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="S32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AS32" t="n">
         <v>2.88</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W32" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG32" t="n">
+      <c r="AT32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD32" t="n">
         <v>3.1</v>
       </c>
-      <c r="AH32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BE32" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,127 +7105,127 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.37</v>
+        <v>1.77</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R34" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="S34" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="T34" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="U34" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="V34" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W34" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="X34" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z34" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI34" t="n">
         <v>9</v>
       </c>
-      <c r="AA34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>7</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
         <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="BE34" t="n">
         <v>1.44</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7311,124 +7311,124 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R37" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="S37" t="n">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="T37" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="U37" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="V37" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="W37" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="X37" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC37" t="n">
         <v>1.22</v>
       </c>
       <c r="AD37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA37" t="n">
         <v>3.4</v>
       </c>
-      <c r="AE37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW37" t="n">
+      <c r="BB37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE37" t="n">
         <v>1.8</v>
       </c>
-      <c r="AX37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BF37" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46099.69791666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="R38" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="S38" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="T38" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="U38" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="V38" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W38" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="X38" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC38" t="n">
         <v>1.22</v>
       </c>
       <c r="AD38" t="n">
-        <v>4</v>
+        <v>3.41</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AI38" t="n">
-        <v>4.65</v>
+        <v>6.21</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE38" t="n">
         <v>1.65</v>
       </c>
-      <c r="AL38" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
+      <c r="BF38" t="n">
         <v>1.17</v>
       </c>
-      <c r="AQ38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46099.69791666666</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="R39" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="S39" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="T39" t="n">
-        <v>2.13</v>
+        <v>2.82</v>
       </c>
       <c r="U39" t="n">
-        <v>4.75</v>
+        <v>6.38</v>
       </c>
       <c r="V39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.37</v>
       </c>
-      <c r="W39" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE39" t="n">
+      <c r="AK39" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT39" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF39" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ39" t="n">
+      <c r="AU39" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>1.1</v>
       </c>
-      <c r="AK39" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.42</v>
-      </c>
       <c r="BA39" t="n">
-        <v>2.83</v>
+        <v>8</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="R40" t="n">
-        <v>8.4</v>
+        <v>4.1</v>
       </c>
       <c r="S40" t="n">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="T40" t="n">
-        <v>2.95</v>
+        <v>2.13</v>
       </c>
       <c r="U40" t="n">
-        <v>6.95</v>
+        <v>4.75</v>
       </c>
       <c r="V40" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="W40" t="n">
-        <v>4.65</v>
+        <v>2.81</v>
       </c>
       <c r="X40" t="n">
-        <v>1.8</v>
+        <v>2.77</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="AF40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BD40" t="n">
         <v>3.4</v>
       </c>
-      <c r="AG40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>5.75</v>
-      </c>
       <c r="BE40" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U41" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W41" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT41" t="n">
         <v>2.55</v>
       </c>
-      <c r="Q41" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U41" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W41" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF41" t="n">
+      <c r="AU41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW41" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG41" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK41" t="n">
+      <c r="AX41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC41" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BD41" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.75</v>
+        <v>3.76</v>
       </c>
       <c r="R42" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="S42" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="U42" t="n">
-        <v>6.38</v>
+        <v>2.99</v>
       </c>
       <c r="V42" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="W42" t="n">
-        <v>4.25</v>
+        <v>3.42</v>
       </c>
       <c r="X42" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.85</v>
+        <v>4</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="AF42" t="n">
-        <v>3.18</v>
+        <v>2.1</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.89</v>
+        <v>2.76</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.98</v>
+        <v>1.42</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
       <c r="AN42" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AT42" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AX42" t="n">
         <v>1.91</v>
       </c>
-      <c r="AU42" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>2</v>
-      </c>
       <c r="AY42" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="BA42" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="BE42" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10257,28 +10257,28 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R50" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S50" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T50" t="n">
         <v>2.15</v>
       </c>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="V50" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W50" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="X50" t="n">
         <v>2.82</v>
@@ -10287,7 +10287,7 @@
         <v>1.35</v>
       </c>
       <c r="Z50" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA50" t="n">
         <v>1.03</v>
@@ -10314,10 +10314,10 @@
         <v>1.29</v>
       </c>
       <c r="AI50" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AK50" t="n">
         <v>1.75</v>
@@ -10326,10 +10326,10 @@
         <v>1.91</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -10383,7 +10383,7 @@
         <v>1.62</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,130 +10454,130 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="R51" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="S51" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="T51" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U51" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="V51" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W51" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="X51" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AD51" t="n">
         <v>3.7</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AH51" t="n">
         <v>1.33</v>
       </c>
       <c r="AI51" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AL51" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB51" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1.19</v>
       </c>
       <c r="BC51" t="n">
         <v>2.05</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BF51" t="n">
         <v>1.18</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,130 +10651,130 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.16</v>
+        <v>3.65</v>
       </c>
       <c r="R52" t="n">
-        <v>5.8</v>
+        <v>3.92</v>
       </c>
       <c r="S52" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="T52" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="V52" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W52" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="X52" t="n">
         <v>2.69</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z52" t="n">
-        <v>5.75</v>
+        <v>6.65</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
         <v>1.95</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AH52" t="n">
         <v>1.33</v>
       </c>
       <c r="AI52" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AM52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="n">
+      <c r="AQ52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB52" t="n">
         <v>1.19</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>1.22</v>
       </c>
       <c r="BC52" t="n">
         <v>2.05</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BF52" t="n">
         <v>1.18</v>
@@ -10848,28 +10848,28 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="R53" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="S53" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="T53" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U53" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="V53" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W53" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="X53" t="n">
         <v>2.94</v>
@@ -10896,10 +10896,10 @@
         <v>2.14</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG53" t="n">
-        <v>3.54</v>
+        <v>3.83</v>
       </c>
       <c r="AH53" t="n">
         <v>1.22</v>
@@ -10908,7 +10908,7 @@
         <v>7.5</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK53" t="n">
         <v>1.8</v>
@@ -10932,40 +10932,40 @@
         <v>1.47</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AS53" t="n">
         <v>2.23</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AV53" t="n">
         <v>2.45</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AX53" t="n">
         <v>1.57</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="BA53" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="BB53" t="n">
         <v>1.29</v>
       </c>
       <c r="BC53" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="BD53" t="n">
         <v>3.3</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="R54" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="S54" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="T54" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U54" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="V54" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W54" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="X54" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AB54" t="n">
         <v>1.06</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.08</v>
+        <v>2.76</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI54" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK54" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AN54" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="AQ54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB54" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR54" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC54" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE54" t="n">
         <v>1.57</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R55" t="n">
+        <v>4</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T55" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.05</v>
-      </c>
       <c r="U55" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="V55" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W55" t="n">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="X55" t="n">
-        <v>3.32</v>
+        <v>3.13</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z55" t="n">
         <v>7</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AG55" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI55" t="n">
-        <v>8.5</v>
+        <v>5.94</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL55" t="n">
         <v>1.85</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AN55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE55" t="n">
         <v>1.57</v>
       </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF55" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11636,22 +11636,22 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="S57" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="T57" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U57" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="V57" t="n">
         <v>1.43</v>
@@ -11660,10 +11660,10 @@
         <v>2.62</v>
       </c>
       <c r="X57" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z57" t="n">
         <v>5.95</v>
@@ -11678,91 +11678,91 @@
         <v>1.25</v>
       </c>
       <c r="AD57" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="AE57" t="n">
         <v>1.85</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG57" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="AH57" t="n">
         <v>1.39</v>
       </c>
       <c r="AI57" t="n">
-        <v>4.95</v>
+        <v>5.86</v>
       </c>
       <c r="AJ57" t="n">
         <v>1.11</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL57" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AM57" t="n">
         <v>1.3</v>
       </c>
       <c r="AN57" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="AT57" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA57" t="n">
         <v>2.43</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>2.8</v>
       </c>
       <c r="BB57" t="n">
         <v>1.2</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11833,61 +11833,61 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="R58" t="n">
-        <v>2.61</v>
+        <v>2.32</v>
       </c>
       <c r="S58" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T58" t="n">
         <v>2.1</v>
       </c>
       <c r="U58" t="n">
-        <v>3.29</v>
+        <v>3.11</v>
       </c>
       <c r="V58" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W58" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="X58" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z58" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="AE58" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AF58" t="n">
         <v>1.73</v>
       </c>
       <c r="AG58" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI58" t="n">
         <v>7</v>
@@ -11902,10 +11902,10 @@
         <v>1.95</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AN58" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
@@ -11917,34 +11917,34 @@
         <v>1.52</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AS58" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AT58" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AU58" t="n">
         <v>3.2</v>
       </c>
       <c r="AV58" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AZ58" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="BB58" t="n">
         <v>1.25</v>
@@ -11959,7 +11959,7 @@
         <v>1.62</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>3.22</v>
+        <v>2.74</v>
       </c>
       <c r="V2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1.47</v>
       </c>
-      <c r="W2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF2" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="S3" t="n">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="U3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>2.73</v>
+        <v>2.36</v>
       </c>
       <c r="X3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD3" t="n">
         <v>2.75</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AE3" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.45</v>
+        <v>9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AW3" t="n">
         <v>1.44</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AX3" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="X4" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AG4" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" t="n">
-        <v>9</v>
+        <v>6.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
         <v>1.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.14</v>
+        <v>2.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.49</v>
+        <v>3.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AU4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC4" t="n">
         <v>2.3</v>
       </c>
-      <c r="AV4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.39</v>
-      </c>
       <c r="BD4" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.15</v>
+        <v>4.1</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>2.51</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="U5" t="n">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>2.58</v>
+        <v>2.73</v>
       </c>
       <c r="X5" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX5" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.25</v>
       </c>
-      <c r="AY5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1983,25 +1983,25 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
         <v>3.28</v>
       </c>
       <c r="R8" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="S8" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>4.55</v>
+        <v>3.89</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
         <v>2.5</v>
@@ -2037,13 +2037,13 @@
         <v>4.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AK8" t="n">
         <v>1.91</v>
@@ -2067,7 +2067,7 @@
         <v>1.84</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="AS8" t="n">
         <v>3.4</v>
@@ -2100,13 +2100,13 @@
         <v>1.33</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF8" t="n">
         <v>1.11</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>4.25</v>
       </c>
       <c r="R16" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>5.75</v>
+        <v>3.7</v>
       </c>
       <c r="S17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG17" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,37 +3953,37 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q18" t="n">
         <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S18" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
         <v>2.4</v>
       </c>
       <c r="U18" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W18" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="X18" t="n">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA18" t="n">
         <v>1.12</v>
@@ -3992,10 +3992,10 @@
         <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AE18" t="n">
         <v>1.57</v>
@@ -4007,25 +4007,25 @@
         <v>2.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AM18" t="n">
         <v>1.18</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>1.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AY18" t="n">
         <v>1.32</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BB18" t="n">
         <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.48</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S20" t="n">
         <v>2.93</v>
       </c>
-      <c r="R20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.66</v>
-      </c>
       <c r="T20" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="U20" t="n">
-        <v>2.9</v>
+        <v>3.56</v>
       </c>
       <c r="V20" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>2.17</v>
+        <v>2.78</v>
       </c>
       <c r="X20" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC20" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.3</v>
+        <v>3.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.3</v>
+        <v>3.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AI20" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.74</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="R26" t="n">
-        <v>2.09</v>
+        <v>2.86</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG26" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.61</v>
+        <v>3.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>2.46</v>
+        <v>1.74</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="U27" t="n">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W27" t="n">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="X27" t="n">
-        <v>2.53</v>
+        <v>2.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.85</v>
+        <v>4.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BD27" t="n">
         <v>5</v>
       </c>
-      <c r="AJ27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE27" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6129,124 +6129,124 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AV30" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH30" t="n">
+      <c r="AW30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BB30" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI30" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BC30" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT33" t="n">
         <v>2.8</v>
       </c>
-      <c r="R33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC33" t="n">
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY33" t="n">
         <v>1.37</v>
       </c>
-      <c r="AD33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL33" t="n">
+      <c r="AZ33" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AV33" t="n">
+      <c r="BA33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC33" t="n">
         <v>2.1</v>
       </c>
-      <c r="AW33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY33" t="n">
+      <c r="BD33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF33" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="S34" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="T34" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="U34" t="n">
-        <v>5</v>
+        <v>5.69</v>
       </c>
       <c r="V34" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W34" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="X34" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA34" t="n">
         <v>1.01</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AC34" t="n">
         <v>1.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AE34" t="n">
         <v>2.25</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI34" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ34" t="n">
         <v>1.05</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7222,16 +7222,16 @@
         <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7499,19 +7499,19 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S36" t="n">
         <v>7.5</v>
       </c>
       <c r="T36" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="U36" t="n">
         <v>1.67</v>
@@ -7547,13 +7547,13 @@
         <v>1.46</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AG36" t="n">
         <v>2.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI36" t="n">
         <v>3.5</v>
@@ -7568,10 +7568,10 @@
         <v>1.85</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7893,43 +7893,43 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="R38" t="n">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="S38" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="T38" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="U38" t="n">
-        <v>4.8</v>
+        <v>5.26</v>
       </c>
       <c r="V38" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W38" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="X38" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z38" t="n">
         <v>7</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC38" t="n">
         <v>1.22</v>
@@ -7938,34 +7938,34 @@
         <v>3.41</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI38" t="n">
         <v>6.21</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AN38" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AO38" t="n">
         <v>1.21</v>
@@ -8007,16 +8007,16 @@
         <v>3.32</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BF38" t="n">
         <v>1.17</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="R40" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="S40" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="T40" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>4.75</v>
+        <v>2.99</v>
       </c>
       <c r="V40" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W40" t="n">
-        <v>2.81</v>
+        <v>3.42</v>
       </c>
       <c r="X40" t="n">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="Z40" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB40" t="n">
-        <v>1</v>
-      </c>
       <c r="AC40" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AD40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA40" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF40" t="n">
+      <c r="BB40" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE40" t="n">
         <v>1.82</v>
       </c>
-      <c r="AG40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BF40" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="R41" t="n">
-        <v>8.4</v>
+        <v>4.1</v>
       </c>
       <c r="S41" t="n">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="T41" t="n">
-        <v>2.95</v>
+        <v>2.13</v>
       </c>
       <c r="U41" t="n">
-        <v>6.95</v>
+        <v>4.75</v>
       </c>
       <c r="V41" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="W41" t="n">
-        <v>4.65</v>
+        <v>2.81</v>
       </c>
       <c r="X41" t="n">
-        <v>1.8</v>
+        <v>2.77</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="AF41" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BD41" t="n">
         <v>3.4</v>
       </c>
-      <c r="AG41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>5.75</v>
-      </c>
       <c r="BE41" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U42" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W42" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT42" t="n">
         <v>2.55</v>
       </c>
-      <c r="Q42" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W42" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF42" t="n">
+      <c r="AU42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW42" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG42" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK42" t="n">
+      <c r="AX42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC42" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL42" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BD42" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10263,13 +10263,13 @@
         <v>3.25</v>
       </c>
       <c r="R50" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="S50" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T50" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="U50" t="n">
         <v>3.7</v>
@@ -10293,31 +10293,31 @@
         <v>1.03</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AE50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF50" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF50" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG50" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AI50" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK50" t="n">
         <v>1.75</v>
@@ -10326,10 +10326,10 @@
         <v>1.91</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -10383,7 +10383,7 @@
         <v>1.62</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10457,7 +10457,7 @@
         <v>1.55</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
         <v>5.5</v>
@@ -10475,19 +10475,19 @@
         <v>1.33</v>
       </c>
       <c r="W51" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="X51" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z51" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AB51" t="n">
         <v>1.01</v>
@@ -10499,7 +10499,7 @@
         <v>3.7</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AF51" t="n">
         <v>1.95</v>
@@ -10517,16 +10517,16 @@
         <v>1.13</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AN51" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -10568,13 +10568,13 @@
         <v>3.7</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BC51" t="n">
         <v>2.05</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="BE51" t="n">
         <v>1.7</v>
@@ -10651,16 +10651,16 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q52" t="n">
         <v>3.65</v>
       </c>
       <c r="R52" t="n">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="S52" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T52" t="n">
         <v>2.25</v>
@@ -10672,19 +10672,19 @@
         <v>1.36</v>
       </c>
       <c r="W52" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="X52" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.65</v>
+        <v>6.25</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB52" t="n">
         <v>1.05</v>
@@ -10693,37 +10693,37 @@
         <v>1.28</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.71</v>
+        <v>3.54</v>
       </c>
       <c r="AE52" t="n">
         <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG52" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AI52" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10768,16 +10768,16 @@
         <v>1.19</v>
       </c>
       <c r="BC52" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10848,10 +10848,10 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R53" t="n">
         <v>2.87</v>
@@ -10860,10 +10860,10 @@
         <v>2.8</v>
       </c>
       <c r="T53" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U53" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V53" t="n">
         <v>1.44</v>
@@ -10872,13 +10872,13 @@
         <v>2.59</v>
       </c>
       <c r="X53" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z53" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="AA53" t="n">
         <v>1.04</v>
@@ -10887,16 +10887,16 @@
         <v>1.06</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD53" t="n">
         <v>3</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG53" t="n">
         <v>3.83</v>
@@ -10908,7 +10908,7 @@
         <v>7.5</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK53" t="n">
         <v>1.8</v>
@@ -10917,7 +10917,7 @@
         <v>1.91</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AN53" t="n">
         <v>1.53</v>
@@ -10962,19 +10962,19 @@
         <v>2.3</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BC53" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11060,34 +11060,34 @@
         <v>2.05</v>
       </c>
       <c r="U54" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="V54" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W54" t="n">
         <v>2.71</v>
       </c>
       <c r="X54" t="n">
-        <v>3.15</v>
+        <v>3.33</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z54" t="n">
         <v>8</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB54" t="n">
         <v>1.06</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="AE54" t="n">
         <v>2.19</v>
@@ -11096,7 +11096,7 @@
         <v>1.65</v>
       </c>
       <c r="AG54" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AH54" t="n">
         <v>1.2</v>
@@ -11111,7 +11111,7 @@
         <v>1.83</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AM54" t="n">
         <v>1.36</v>
@@ -11123,34 +11123,34 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AR54" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AT54" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AU54" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AZ54" t="n">
         <v>1.6</v>
@@ -11159,19 +11159,19 @@
         <v>2.7</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11242,22 +11242,22 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R55" t="n">
-        <v>4</v>
+        <v>5.06</v>
       </c>
       <c r="S55" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="T55" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="U55" t="n">
-        <v>4.8</v>
+        <v>5.45</v>
       </c>
       <c r="V55" t="n">
         <v>1.42</v>
@@ -11266,55 +11266,55 @@
         <v>2.65</v>
       </c>
       <c r="X55" t="n">
-        <v>3.13</v>
+        <v>2.8</v>
       </c>
       <c r="Y55" t="n">
         <v>1.35</v>
       </c>
       <c r="Z55" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AE55" t="n">
         <v>2.07</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.71</v>
+        <v>3.54</v>
       </c>
       <c r="AH55" t="n">
         <v>1.22</v>
       </c>
       <c r="AI55" t="n">
-        <v>5.94</v>
+        <v>7.5</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN55" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
@@ -11356,19 +11356,19 @@
         <v>3.25</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BC55" t="n">
         <v>2.3</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q56" t="n">
         <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.33</v>
+        <v>2.76</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="S57" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="T57" t="n">
         <v>2.15</v>
       </c>
       <c r="U57" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="V57" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W57" t="n">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="X57" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z57" t="n">
-        <v>5.95</v>
+        <v>7.6</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH57" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD57" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="AE57" t="n">
+      <c r="AI57" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW57" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF57" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
+      <c r="AX57" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB57" t="n">
         <v>1.25</v>
       </c>
-      <c r="AQ57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC57" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="BD57" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,133 +11833,133 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.86</v>
+        <v>2.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="R58" t="n">
-        <v>2.32</v>
+        <v>3.34</v>
       </c>
       <c r="S58" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="T58" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U58" t="n">
-        <v>3.11</v>
+        <v>3.65</v>
       </c>
       <c r="V58" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="W58" t="n">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="X58" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z58" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC58" t="n">
         <v>1.28</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
       <c r="AE58" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="AG58" t="n">
-        <v>3.6</v>
+        <v>2.76</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AI58" t="n">
-        <v>7</v>
+        <v>5.81</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL58" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN58" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AS58" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AT58" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AU58" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AV58" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AZ58" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC58" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="BD58" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>

--- a/jogos_2026-03-18.xlsx
+++ b/jogos_2026-03-18.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="R2" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="X2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AB2" t="n">
         <v>1.06</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN2" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>1.95</v>
       </c>
-      <c r="AL2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
+      <c r="AR2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AW2" t="n">
         <v>1.49</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AX2" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
         <v>2.75</v>
@@ -1010,7 +1010,7 @@
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>3.5</v>
@@ -1034,7 +1034,7 @@
         <v>1.02</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC3" t="n">
         <v>1.4</v>
@@ -1046,19 +1046,19 @@
         <v>2.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AH3" t="n">
         <v>1.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AK3" t="n">
         <v>1.91</v>
@@ -1067,7 +1067,7 @@
         <v>1.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
         <v>1.44</v>
@@ -1076,55 +1076,55 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.14</v>
+        <v>2.47</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.49</v>
+        <v>3.36</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.25</v>
+        <v>5.02</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.3</v>
+   